--- a/ref/Kent U12 & U14 - Waterfall Groups & Fixtures.xlsx
+++ b/ref/Kent U12 & U14 - Waterfall Groups & Fixtures.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hayfincapital-my.sharepoint.com/personal/jennera_hayfin_com/Documents/Personal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="837" documentId="13_ncr:1_{04C4C9B1-5A14-4A20-9F11-0BF762162411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61EB0752-1921-4A46-82FA-D611AC3D4DF3}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="13_ncr:1_{546CE6D7-4214-4E20-B601-B87857BCE646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB983C01-BCB1-40B8-8134-DFE7C716993C}"/>
   <bookViews>
-    <workbookView xWindow="14740" yWindow="-21600" windowWidth="25780" windowHeight="20970" activeTab="1" xr2:uid="{95AFDE92-B225-4D6C-8D47-E4ADDF1C9E58}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{95AFDE92-B225-4D6C-8D47-E4ADDF1C9E58}"/>
   </bookViews>
   <sheets>
     <sheet name="U14 Waterfall Fixtures" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1643" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="269">
   <si>
     <t>TJ's</t>
   </si>
@@ -549,9 +549,6 @@
     <t>Blackheath U14 Boys</t>
   </si>
   <si>
-    <t>Old Colfeians U14</t>
-  </si>
-  <si>
     <t>Aylesford Bulls U14s</t>
   </si>
   <si>
@@ -696,9 +693,6 @@
     <t>Dover RFC</t>
   </si>
   <si>
-    <t>Ashford RFC</t>
-  </si>
-  <si>
     <t>Whitstable RFC</t>
   </si>
   <si>
@@ -853,6 +847,9 @@
   </si>
   <si>
     <t>Dartford Valley RFC : Dartford Valley RFC U12</t>
+  </si>
+  <si>
+    <t>WO</t>
   </si>
 </sst>
 </file>
@@ -1355,7 +1352,7 @@
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="261">
+  <cellXfs count="260">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1955,6 +1952,8 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2000,9 +1999,6 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
@@ -2422,153 +2418,153 @@
     </row>
     <row r="2" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="19"/>
-      <c r="B2" s="243" t="s">
+      <c r="B2" s="245" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="248"/>
-      <c r="D2" s="248"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
-      <c r="G2" s="248"/>
-      <c r="H2" s="248"/>
-      <c r="I2" s="248"/>
-      <c r="J2" s="249"/>
+      <c r="C2" s="250"/>
+      <c r="D2" s="250"/>
+      <c r="E2" s="250"/>
+      <c r="F2" s="250"/>
+      <c r="G2" s="250"/>
+      <c r="H2" s="250"/>
+      <c r="I2" s="250"/>
+      <c r="J2" s="251"/>
       <c r="M2" s="19"/>
-      <c r="N2" s="243" t="s">
+      <c r="N2" s="245" t="s">
         <v>61</v>
       </c>
-      <c r="O2" s="248"/>
-      <c r="P2" s="248"/>
-      <c r="Q2" s="248"/>
-      <c r="R2" s="248"/>
-      <c r="S2" s="248"/>
-      <c r="T2" s="248"/>
-      <c r="U2" s="248"/>
-      <c r="V2" s="249"/>
+      <c r="O2" s="250"/>
+      <c r="P2" s="250"/>
+      <c r="Q2" s="250"/>
+      <c r="R2" s="250"/>
+      <c r="S2" s="250"/>
+      <c r="T2" s="250"/>
+      <c r="U2" s="250"/>
+      <c r="V2" s="251"/>
       <c r="W2" s="19"/>
-      <c r="X2" s="243" t="s">
+      <c r="X2" s="245" t="s">
         <v>98</v>
       </c>
-      <c r="Y2" s="244"/>
-      <c r="Z2" s="244"/>
-      <c r="AA2" s="244"/>
-      <c r="AB2" s="244"/>
-      <c r="AC2" s="244"/>
-      <c r="AD2" s="244"/>
-      <c r="AE2" s="244"/>
-      <c r="AF2" s="244"/>
-      <c r="AG2" s="245"/>
+      <c r="Y2" s="246"/>
+      <c r="Z2" s="246"/>
+      <c r="AA2" s="246"/>
+      <c r="AB2" s="246"/>
+      <c r="AC2" s="246"/>
+      <c r="AD2" s="246"/>
+      <c r="AE2" s="246"/>
+      <c r="AF2" s="246"/>
+      <c r="AG2" s="247"/>
       <c r="AH2" s="19"/>
-      <c r="AI2" s="243" t="s">
+      <c r="AI2" s="245" t="s">
         <v>128</v>
       </c>
-      <c r="AJ2" s="244"/>
-      <c r="AK2" s="244"/>
-      <c r="AL2" s="244"/>
-      <c r="AM2" s="244"/>
-      <c r="AN2" s="244"/>
-      <c r="AO2" s="244"/>
-      <c r="AP2" s="244"/>
-      <c r="AQ2" s="244"/>
-      <c r="AR2" s="245"/>
+      <c r="AJ2" s="246"/>
+      <c r="AK2" s="246"/>
+      <c r="AL2" s="246"/>
+      <c r="AM2" s="246"/>
+      <c r="AN2" s="246"/>
+      <c r="AO2" s="246"/>
+      <c r="AP2" s="246"/>
+      <c r="AQ2" s="246"/>
+      <c r="AR2" s="247"/>
       <c r="AS2" s="19"/>
-      <c r="AT2" s="243" t="s">
+      <c r="AT2" s="245" t="s">
         <v>149</v>
       </c>
-      <c r="AU2" s="244"/>
-      <c r="AV2" s="244"/>
-      <c r="AW2" s="244"/>
-      <c r="AX2" s="244"/>
-      <c r="AY2" s="244"/>
-      <c r="AZ2" s="244"/>
-      <c r="BA2" s="244"/>
-      <c r="BB2" s="244"/>
-      <c r="BC2" s="245"/>
+      <c r="AU2" s="246"/>
+      <c r="AV2" s="246"/>
+      <c r="AW2" s="246"/>
+      <c r="AX2" s="246"/>
+      <c r="AY2" s="246"/>
+      <c r="AZ2" s="246"/>
+      <c r="BA2" s="246"/>
+      <c r="BB2" s="246"/>
+      <c r="BC2" s="247"/>
     </row>
     <row r="3" spans="1:60" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="19"/>
       <c r="B3" s="115"/>
-      <c r="C3" s="246" t="s">
+      <c r="C3" s="248" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="246"/>
+      <c r="D3" s="248"/>
       <c r="E3" s="114"/>
       <c r="F3" s="198" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="246" t="s">
+      <c r="G3" s="248" t="s">
         <v>59</v>
       </c>
-      <c r="H3" s="246"/>
-      <c r="I3" s="246"/>
-      <c r="J3" s="247"/>
+      <c r="H3" s="248"/>
+      <c r="I3" s="248"/>
+      <c r="J3" s="249"/>
       <c r="M3" s="19"/>
       <c r="N3" s="115"/>
-      <c r="O3" s="246" t="s">
+      <c r="O3" s="248" t="s">
         <v>58</v>
       </c>
-      <c r="P3" s="246"/>
+      <c r="P3" s="248"/>
       <c r="Q3" s="114"/>
       <c r="R3" s="113" t="s">
         <v>57</v>
       </c>
-      <c r="S3" s="246" t="s">
+      <c r="S3" s="248" t="s">
         <v>56</v>
       </c>
-      <c r="T3" s="246"/>
-      <c r="U3" s="246"/>
-      <c r="V3" s="247"/>
+      <c r="T3" s="248"/>
+      <c r="U3" s="248"/>
+      <c r="V3" s="249"/>
       <c r="W3" s="19"/>
-      <c r="X3" s="243" t="s">
+      <c r="X3" s="245" t="s">
         <v>58</v>
       </c>
-      <c r="Y3" s="244"/>
-      <c r="Z3" s="244"/>
-      <c r="AA3" s="244"/>
+      <c r="Y3" s="246"/>
+      <c r="Z3" s="246"/>
+      <c r="AA3" s="246"/>
       <c r="AB3" s="198" t="s">
         <v>57</v>
       </c>
-      <c r="AC3" s="246" t="s">
+      <c r="AC3" s="248" t="s">
         <v>56</v>
       </c>
-      <c r="AD3" s="250"/>
-      <c r="AE3" s="250"/>
-      <c r="AF3" s="250"/>
-      <c r="AG3" s="251"/>
+      <c r="AD3" s="252"/>
+      <c r="AE3" s="252"/>
+      <c r="AF3" s="252"/>
+      <c r="AG3" s="253"/>
       <c r="AH3" s="19"/>
-      <c r="AI3" s="243" t="s">
+      <c r="AI3" s="245" t="s">
         <v>58</v>
       </c>
-      <c r="AJ3" s="244"/>
-      <c r="AK3" s="244"/>
-      <c r="AL3" s="244"/>
+      <c r="AJ3" s="246"/>
+      <c r="AK3" s="246"/>
+      <c r="AL3" s="246"/>
       <c r="AM3" s="198" t="s">
         <v>57</v>
       </c>
-      <c r="AN3" s="246" t="s">
+      <c r="AN3" s="248" t="s">
         <v>56</v>
       </c>
-      <c r="AO3" s="250"/>
-      <c r="AP3" s="250"/>
-      <c r="AQ3" s="250"/>
-      <c r="AR3" s="251"/>
+      <c r="AO3" s="252"/>
+      <c r="AP3" s="252"/>
+      <c r="AQ3" s="252"/>
+      <c r="AR3" s="253"/>
       <c r="AS3" s="19"/>
-      <c r="AT3" s="243" t="s">
+      <c r="AT3" s="245" t="s">
         <v>58</v>
       </c>
-      <c r="AU3" s="244"/>
-      <c r="AV3" s="244"/>
-      <c r="AW3" s="244"/>
+      <c r="AU3" s="246"/>
+      <c r="AV3" s="246"/>
+      <c r="AW3" s="246"/>
       <c r="AX3" s="198" t="s">
         <v>57</v>
       </c>
-      <c r="AY3" s="246" t="s">
+      <c r="AY3" s="248" t="s">
         <v>56</v>
       </c>
-      <c r="AZ3" s="250"/>
-      <c r="BA3" s="250"/>
-      <c r="BB3" s="250"/>
-      <c r="BC3" s="251"/>
+      <c r="AZ3" s="252"/>
+      <c r="BA3" s="252"/>
+      <c r="BB3" s="252"/>
+      <c r="BC3" s="253"/>
     </row>
     <row r="4" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="19"/>
@@ -2647,8 +2643,7 @@
       <c r="BA4" s="134"/>
       <c r="BB4" s="134"/>
       <c r="BC4" s="139"/>
-      <c r="BE4" s="258"/>
-      <c r="BF4" s="259"/>
+      <c r="BF4" s="243"/>
     </row>
     <row r="5" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="19"/>
@@ -2759,16 +2754,19 @@
         <v>46292</v>
       </c>
       <c r="AY5" s="136" t="s">
-        <v>201</v>
-      </c>
-      <c r="AZ5" s="138"/>
-      <c r="BA5" s="138"/>
+        <v>200</v>
+      </c>
+      <c r="AZ5" s="138">
+        <v>38</v>
+      </c>
+      <c r="BA5" s="138">
+        <v>12</v>
+      </c>
       <c r="BB5" s="138" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="BC5" s="149"/>
-      <c r="BE5" s="258"/>
-      <c r="BF5" s="259"/>
+      <c r="BF5" s="243"/>
     </row>
     <row r="6" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="19"/>
@@ -2868,24 +2866,28 @@
       <c r="AS6" s="19"/>
       <c r="AT6" s="181"/>
       <c r="AU6" s="138" t="s">
-        <v>150</v>
-      </c>
-      <c r="AV6" s="139"/>
+        <v>151</v>
+      </c>
+      <c r="AV6" s="139">
+        <v>5</v>
+      </c>
       <c r="AW6" s="141"/>
       <c r="AX6" s="184">
         <v>46292</v>
       </c>
       <c r="AY6" s="159" t="s">
-        <v>202</v>
-      </c>
-      <c r="AZ6" s="155"/>
-      <c r="BA6" s="155"/>
+        <v>201</v>
+      </c>
+      <c r="AZ6" s="155">
+        <v>45</v>
+      </c>
+      <c r="BA6" s="155">
+        <v>12</v>
+      </c>
       <c r="BB6" s="155" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BC6" s="149"/>
-      <c r="BE6" s="258"/>
-      <c r="BF6" s="258"/>
     </row>
     <row r="7" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="19"/>
@@ -2985,24 +2987,24 @@
       <c r="AS7" s="19"/>
       <c r="AT7" s="181"/>
       <c r="AU7" s="147" t="s">
-        <v>151</v>
-      </c>
-      <c r="AV7" s="149"/>
+        <v>154</v>
+      </c>
+      <c r="AV7" s="149">
+        <v>5</v>
+      </c>
       <c r="AW7" s="141"/>
       <c r="AX7" s="183">
         <v>46306</v>
       </c>
       <c r="AY7" s="136" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AZ7" s="138"/>
       <c r="BA7" s="138"/>
       <c r="BB7" s="138" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="BC7" s="149"/>
-      <c r="BE7" s="258"/>
-      <c r="BF7" s="258"/>
     </row>
     <row r="8" spans="1:60" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="19"/>
@@ -3108,22 +3110,22 @@
       <c r="AU8" s="147" t="s">
         <v>152</v>
       </c>
-      <c r="AV8" s="149"/>
+      <c r="AV8" s="149">
+        <v>1</v>
+      </c>
       <c r="AW8" s="141"/>
       <c r="AX8" s="184">
         <v>46306</v>
       </c>
       <c r="AY8" s="159" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AZ8" s="155"/>
       <c r="BA8" s="155"/>
       <c r="BB8" s="155" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="BC8" s="149"/>
-      <c r="BE8" s="258"/>
-      <c r="BF8" s="258"/>
     </row>
     <row r="9" spans="1:60" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="19"/>
@@ -3229,22 +3231,22 @@
       <c r="AU9" s="147" t="s">
         <v>153</v>
       </c>
-      <c r="AV9" s="149"/>
+      <c r="AV9" s="149">
+        <v>1</v>
+      </c>
       <c r="AW9" s="141"/>
       <c r="AX9" s="183">
         <v>46341</v>
       </c>
       <c r="AY9" s="136" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AZ9" s="138"/>
       <c r="BA9" s="138"/>
       <c r="BB9" s="138" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="BC9" s="149"/>
-      <c r="BE9" s="258"/>
-      <c r="BF9" s="258"/>
     </row>
     <row r="10" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="19"/>
@@ -3326,7 +3328,7 @@
       <c r="AS10" s="19"/>
       <c r="AT10" s="181"/>
       <c r="AU10" s="155" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="AV10" s="164"/>
       <c r="AW10" s="141"/>
@@ -3334,16 +3336,14 @@
         <v>46341</v>
       </c>
       <c r="AY10" s="159" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AZ10" s="155"/>
       <c r="BA10" s="155"/>
       <c r="BB10" s="155" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BC10" s="149"/>
-      <c r="BE10" s="258"/>
-      <c r="BF10" s="258"/>
     </row>
     <row r="11" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A11" s="19"/>
@@ -3411,16 +3411,14 @@
         <v>46355</v>
       </c>
       <c r="AY11" s="136" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AZ11" s="138"/>
       <c r="BA11" s="138"/>
       <c r="BB11" s="138" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="BC11" s="149"/>
-      <c r="BE11" s="258"/>
-      <c r="BF11" s="258"/>
     </row>
     <row r="12" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="19"/>
@@ -3501,16 +3499,14 @@
         <v>46355</v>
       </c>
       <c r="AY12" s="159" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AZ12" s="155"/>
       <c r="BA12" s="155"/>
       <c r="BB12" s="155" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="BC12" s="149"/>
-      <c r="BE12" s="258"/>
-      <c r="BF12" s="258"/>
     </row>
     <row r="13" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A13" s="19"/>
@@ -3591,16 +3587,14 @@
         <v>46369</v>
       </c>
       <c r="AY13" s="136" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AZ13" s="138"/>
       <c r="BA13" s="138"/>
       <c r="BB13" s="138" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="BC13" s="149"/>
-      <c r="BE13" s="258"/>
-      <c r="BF13" s="258"/>
     </row>
     <row r="14" spans="1:60" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="19"/>
@@ -3713,16 +3707,14 @@
         <v>46369</v>
       </c>
       <c r="AY14" s="159" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AZ14" s="155"/>
       <c r="BA14" s="155"/>
       <c r="BB14" s="155" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="BC14" s="149"/>
-      <c r="BE14" s="258"/>
-      <c r="BF14" s="258"/>
     </row>
     <row r="15" spans="1:60" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A15" s="19"/>
@@ -3833,8 +3825,6 @@
       <c r="BA15" s="162"/>
       <c r="BB15" s="162"/>
       <c r="BC15" s="149"/>
-      <c r="BE15" s="258"/>
-      <c r="BF15" s="258"/>
     </row>
     <row r="16" spans="1:60" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A16" s="19"/>
@@ -3942,10 +3932,8 @@
       <c r="BA16" s="117"/>
       <c r="BB16" s="118"/>
       <c r="BC16" s="118"/>
-      <c r="BE16" s="258"/>
-      <c r="BF16" s="258"/>
-    </row>
-    <row r="17" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="17" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A17" s="19"/>
       <c r="B17" s="140"/>
       <c r="C17" s="146" t="s">
@@ -4051,10 +4039,8 @@
       <c r="BA17" s="134"/>
       <c r="BB17" s="134"/>
       <c r="BC17" s="139"/>
-      <c r="BE17" s="258"/>
-      <c r="BF17" s="258"/>
-    </row>
-    <row r="18" spans="1:58" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="18" spans="1:55" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A18" s="19"/>
       <c r="B18" s="140"/>
       <c r="C18" s="146" t="s">
@@ -4162,18 +4148,20 @@
         <v>46292</v>
       </c>
       <c r="AY18" s="136" t="s">
-        <v>208</v>
-      </c>
-      <c r="AZ18" s="138"/>
-      <c r="BA18" s="138"/>
+        <v>207</v>
+      </c>
+      <c r="AZ18" s="138">
+        <v>38</v>
+      </c>
+      <c r="BA18" s="138">
+        <v>0</v>
+      </c>
       <c r="BB18" s="138" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="BC18" s="149"/>
-      <c r="BE18" s="258"/>
-      <c r="BF18" s="258"/>
-    </row>
-    <row r="19" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="19" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A19" s="19"/>
       <c r="B19" s="140"/>
       <c r="C19" s="154" t="s">
@@ -4255,24 +4243,28 @@
       <c r="AU19" s="220" t="s">
         <v>155</v>
       </c>
-      <c r="AV19" s="139"/>
+      <c r="AV19" s="139">
+        <v>5</v>
+      </c>
       <c r="AW19" s="141"/>
       <c r="AX19" s="184">
         <v>46292</v>
       </c>
       <c r="AY19" s="159" t="s">
-        <v>209</v>
-      </c>
-      <c r="AZ19" s="155"/>
-      <c r="BA19" s="155"/>
+        <v>208</v>
+      </c>
+      <c r="AZ19" s="155">
+        <v>22</v>
+      </c>
+      <c r="BA19" s="155">
+        <v>12</v>
+      </c>
       <c r="BB19" s="155" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="BC19" s="149"/>
-      <c r="BE19" s="258"/>
-      <c r="BF19" s="258"/>
-    </row>
-    <row r="20" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="20" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A20" s="19"/>
       <c r="B20" s="140"/>
       <c r="C20" s="162"/>
@@ -4338,26 +4330,26 @@
       <c r="AS20" s="19"/>
       <c r="AT20" s="181"/>
       <c r="AU20" s="147" t="s">
-        <v>146</v>
-      </c>
-      <c r="AV20" s="149"/>
+        <v>157</v>
+      </c>
+      <c r="AV20" s="149">
+        <v>5</v>
+      </c>
       <c r="AW20" s="141"/>
       <c r="AX20" s="183">
         <v>46306</v>
       </c>
       <c r="AY20" s="136" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AZ20" s="138"/>
       <c r="BA20" s="138"/>
       <c r="BB20" s="138" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="BC20" s="149"/>
-      <c r="BE20" s="258"/>
-      <c r="BF20" s="258"/>
-    </row>
-    <row r="21" spans="1:58" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="21" spans="1:55" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A21" s="19"/>
       <c r="B21" s="156"/>
       <c r="C21" s="157"/>
@@ -4425,24 +4417,24 @@
       <c r="AU21" s="147" t="s">
         <v>156</v>
       </c>
-      <c r="AV21" s="149"/>
+      <c r="AV21" s="149">
+        <v>1</v>
+      </c>
       <c r="AW21" s="141"/>
       <c r="AX21" s="184">
         <v>46306</v>
       </c>
       <c r="AY21" s="159" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AZ21" s="155"/>
       <c r="BA21" s="155"/>
       <c r="BB21" s="155" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="BC21" s="149"/>
-      <c r="BE21" s="258"/>
-      <c r="BF21" s="258"/>
-    </row>
-    <row r="22" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="22" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A22" s="19"/>
       <c r="B22" s="21"/>
       <c r="C22" s="20"/>
@@ -4500,24 +4492,24 @@
       <c r="AU22" s="147" t="s">
         <v>15</v>
       </c>
-      <c r="AV22" s="149"/>
+      <c r="AV22" s="149">
+        <v>1</v>
+      </c>
       <c r="AW22" s="141"/>
       <c r="AX22" s="183">
         <v>46341</v>
       </c>
       <c r="AY22" s="136" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AZ22" s="138"/>
       <c r="BA22" s="138"/>
       <c r="BB22" s="138" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BC22" s="149"/>
-      <c r="BE22" s="258"/>
-      <c r="BF22" s="258"/>
-    </row>
-    <row r="23" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="23" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23" s="19"/>
       <c r="B23" s="133"/>
       <c r="C23" s="134"/>
@@ -4612,7 +4604,7 @@
       <c r="AS23" s="19"/>
       <c r="AT23" s="181"/>
       <c r="AU23" s="155" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="AV23" s="164"/>
       <c r="AW23" s="141"/>
@@ -4620,18 +4612,16 @@
         <v>46341</v>
       </c>
       <c r="AY23" s="159" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AZ23" s="155"/>
       <c r="BA23" s="155"/>
       <c r="BB23" s="155" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="BC23" s="149"/>
-      <c r="BE23" s="258"/>
-      <c r="BF23" s="258"/>
-    </row>
-    <row r="24" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="24" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A24" s="19"/>
       <c r="B24" s="140"/>
       <c r="C24" s="141"/>
@@ -4738,18 +4728,16 @@
         <v>46355</v>
       </c>
       <c r="AY24" s="136" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AZ24" s="138"/>
       <c r="BA24" s="138"/>
       <c r="BB24" s="138" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BC24" s="149"/>
-      <c r="BE24" s="258"/>
-      <c r="BF24" s="258"/>
-    </row>
-    <row r="25" spans="1:58" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="25" spans="1:55" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A25" s="19"/>
       <c r="B25" s="140"/>
       <c r="C25" s="179" t="s">
@@ -4858,18 +4846,16 @@
         <v>46355</v>
       </c>
       <c r="AY25" s="159" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AZ25" s="155"/>
       <c r="BA25" s="155"/>
       <c r="BB25" s="155" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BC25" s="149"/>
-      <c r="BE25" s="258"/>
-      <c r="BF25" s="258"/>
-    </row>
-    <row r="26" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="26" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A26" s="19"/>
       <c r="B26" s="140"/>
       <c r="C26" s="147" t="s">
@@ -4977,18 +4963,16 @@
         <v>46369</v>
       </c>
       <c r="AY26" s="136" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AZ26" s="138"/>
       <c r="BA26" s="138"/>
       <c r="BB26" s="138" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="BC26" s="149"/>
-      <c r="BE26" s="258"/>
-      <c r="BF26" s="258"/>
-    </row>
-    <row r="27" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="27" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A27" s="19"/>
       <c r="B27" s="140"/>
       <c r="C27" s="147" t="s">
@@ -5096,18 +5080,16 @@
         <v>46369</v>
       </c>
       <c r="AY27" s="159" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AZ27" s="155"/>
       <c r="BA27" s="155"/>
       <c r="BB27" s="155" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="BC27" s="149"/>
-      <c r="BE27" s="258"/>
-      <c r="BF27" s="258"/>
-    </row>
-    <row r="28" spans="1:58" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="28" spans="1:55" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A28" s="19"/>
       <c r="B28" s="140"/>
       <c r="C28" s="147" t="s">
@@ -5209,10 +5191,8 @@
       <c r="BA28" s="162"/>
       <c r="BB28" s="162"/>
       <c r="BC28" s="149"/>
-      <c r="BE28" s="258"/>
-      <c r="BF28" s="258"/>
-    </row>
-    <row r="29" spans="1:58" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="29" spans="1:55" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A29" s="19"/>
       <c r="B29" s="140"/>
       <c r="C29" s="147" t="s">
@@ -5294,10 +5274,8 @@
       <c r="BA29" s="197"/>
       <c r="BB29" s="197"/>
       <c r="BC29" s="63"/>
-      <c r="BE29" s="258"/>
-      <c r="BF29" s="258"/>
-    </row>
-    <row r="30" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="30" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A30" s="19"/>
       <c r="B30" s="140"/>
       <c r="C30" s="155" t="s">
@@ -5379,10 +5357,8 @@
       <c r="BA30" s="134"/>
       <c r="BB30" s="134"/>
       <c r="BC30" s="139"/>
-      <c r="BE30" s="258"/>
-      <c r="BF30" s="258"/>
-    </row>
-    <row r="31" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="31" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A31" s="19"/>
       <c r="B31" s="140"/>
       <c r="C31" s="162"/>
@@ -5454,22 +5430,18 @@
         <v>4</v>
       </c>
       <c r="AW31" s="141"/>
-      <c r="AX31" s="183">
-        <v>46292</v>
-      </c>
+      <c r="AX31" s="183"/>
       <c r="AY31" s="136" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AZ31" s="138"/>
       <c r="BA31" s="138"/>
       <c r="BB31" s="138" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="BC31" s="149"/>
-      <c r="BE31" s="258"/>
-      <c r="BF31" s="258"/>
-    </row>
-    <row r="32" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="32" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A32" s="19"/>
       <c r="B32" s="156"/>
       <c r="C32" s="157"/>
@@ -5567,22 +5539,18 @@
       </c>
       <c r="AV32" s="139"/>
       <c r="AW32" s="141"/>
-      <c r="AX32" s="184">
-        <v>46292</v>
-      </c>
+      <c r="AX32" s="184"/>
       <c r="AY32" s="159" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AZ32" s="155"/>
       <c r="BA32" s="155"/>
       <c r="BB32" s="155" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="BC32" s="149"/>
-      <c r="BE32" s="258"/>
-      <c r="BF32" s="258"/>
-    </row>
-    <row r="33" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="33" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A33" s="19"/>
       <c r="B33" s="20"/>
       <c r="C33" s="20"/>
@@ -5674,18 +5642,16 @@
         <v>46306</v>
       </c>
       <c r="AY33" s="136" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AZ33" s="138"/>
       <c r="BA33" s="138"/>
       <c r="BB33" s="138" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="BC33" s="149"/>
-      <c r="BE33" s="258"/>
-      <c r="BF33" s="258"/>
-    </row>
-    <row r="34" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="34" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A34" s="19"/>
       <c r="B34" s="133"/>
       <c r="C34" s="134"/>
@@ -5790,18 +5756,16 @@
         <v>46306</v>
       </c>
       <c r="AY34" s="159" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AZ34" s="155"/>
       <c r="BA34" s="155"/>
       <c r="BB34" s="155" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="BC34" s="149"/>
-      <c r="BE34" s="258"/>
-      <c r="BF34" s="258"/>
-    </row>
-    <row r="35" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="35" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A35" s="19"/>
       <c r="B35" s="140"/>
       <c r="C35" s="178" t="s">
@@ -5898,18 +5862,16 @@
         <v>46341</v>
       </c>
       <c r="AY35" s="136" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AZ35" s="138"/>
       <c r="BA35" s="138"/>
       <c r="BB35" s="138" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="BC35" s="149"/>
-      <c r="BE35" s="258"/>
-      <c r="BF35" s="258"/>
-    </row>
-    <row r="36" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="36" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A36" s="19"/>
       <c r="B36" s="140"/>
       <c r="C36" s="146" t="s">
@@ -6015,18 +5977,16 @@
         <v>46341</v>
       </c>
       <c r="AY36" s="159" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AZ36" s="155"/>
       <c r="BA36" s="155"/>
       <c r="BB36" s="155" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="BC36" s="149"/>
-      <c r="BE36" s="258"/>
-      <c r="BF36" s="258"/>
-    </row>
-    <row r="37" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="37" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A37" s="19"/>
       <c r="B37" s="140"/>
       <c r="C37" s="146" t="s">
@@ -6122,18 +6082,16 @@
         <v>46355</v>
       </c>
       <c r="AY37" s="136" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AZ37" s="138"/>
       <c r="BA37" s="138"/>
       <c r="BB37" s="138" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="BC37" s="149"/>
-      <c r="BE37" s="258"/>
-      <c r="BF37" s="258"/>
-    </row>
-    <row r="38" spans="1:58" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="38" spans="1:55" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A38" s="19"/>
       <c r="B38" s="140"/>
       <c r="C38" s="146" t="s">
@@ -6209,18 +6167,16 @@
         <v>46355</v>
       </c>
       <c r="AY38" s="159" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AZ38" s="155"/>
       <c r="BA38" s="155"/>
       <c r="BB38" s="155" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="BC38" s="149"/>
-      <c r="BE38" s="258"/>
-      <c r="BF38" s="258"/>
-    </row>
-    <row r="39" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="39" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A39" s="19"/>
       <c r="B39" s="140"/>
       <c r="C39" s="154" t="s">
@@ -6296,18 +6252,16 @@
         <v>46369</v>
       </c>
       <c r="AY39" s="136" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AZ39" s="138"/>
       <c r="BA39" s="138"/>
       <c r="BB39" s="138" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="BC39" s="149"/>
-      <c r="BE39" s="258"/>
-      <c r="BF39" s="258"/>
-    </row>
-    <row r="40" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="40" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A40" s="19"/>
       <c r="B40" s="140"/>
       <c r="C40" s="162"/>
@@ -6373,18 +6327,16 @@
         <v>46369</v>
       </c>
       <c r="AY40" s="159" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AZ40" s="155"/>
       <c r="BA40" s="155"/>
       <c r="BB40" s="155" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="BC40" s="149"/>
-      <c r="BE40" s="258"/>
-      <c r="BF40" s="258"/>
-    </row>
-    <row r="41" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="41" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A41" s="19"/>
       <c r="B41" s="156"/>
       <c r="C41" s="157"/>
@@ -6480,10 +6432,8 @@
       <c r="BA41" s="162"/>
       <c r="BB41" s="162"/>
       <c r="BC41" s="149"/>
-      <c r="BE41" s="258"/>
-      <c r="BF41" s="258"/>
-    </row>
-    <row r="42" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="42" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A42" s="19"/>
       <c r="B42" s="21"/>
       <c r="C42" s="20"/>
@@ -6579,10 +6529,8 @@
       <c r="BA42" s="120"/>
       <c r="BB42" s="120"/>
       <c r="BC42" s="119"/>
-      <c r="BE42" s="258"/>
-      <c r="BF42" s="258"/>
-    </row>
-    <row r="43" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="43" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A43" s="19"/>
       <c r="B43" s="133"/>
       <c r="C43" s="134"/>
@@ -6691,10 +6639,8 @@
       <c r="BA43" s="182"/>
       <c r="BB43" s="182"/>
       <c r="BC43" s="192"/>
-      <c r="BE43" s="258"/>
-      <c r="BF43" s="258"/>
-    </row>
-    <row r="44" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="44" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A44" s="19"/>
       <c r="B44" s="140"/>
       <c r="C44" s="162"/>
@@ -6802,18 +6748,20 @@
         <v>46292</v>
       </c>
       <c r="AY44" s="136" t="s">
-        <v>214</v>
-      </c>
-      <c r="AZ44" s="138"/>
-      <c r="BA44" s="138"/>
+        <v>213</v>
+      </c>
+      <c r="AZ44" s="138">
+        <v>5</v>
+      </c>
+      <c r="BA44" s="138">
+        <v>28</v>
+      </c>
       <c r="BB44" s="138" t="s">
-        <v>211</v>
+        <v>171</v>
       </c>
       <c r="BC44" s="149"/>
-      <c r="BE44" s="258"/>
-      <c r="BF44" s="258"/>
-    </row>
-    <row r="45" spans="1:58" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="45" spans="1:55" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A45" s="19"/>
       <c r="B45" s="140"/>
       <c r="C45" s="178" t="s">
@@ -6918,26 +6866,26 @@
       <c r="AS45" s="19"/>
       <c r="AT45" s="181"/>
       <c r="AU45" s="138" t="s">
-        <v>166</v>
-      </c>
-      <c r="AV45" s="139"/>
+        <v>171</v>
+      </c>
+      <c r="AV45" s="139">
+        <v>5</v>
+      </c>
       <c r="AW45" s="141"/>
-      <c r="AX45" s="184">
-        <v>46292</v>
-      </c>
-      <c r="AY45" s="159" t="s">
-        <v>213</v>
-      </c>
-      <c r="AZ45" s="155"/>
-      <c r="BA45" s="155"/>
-      <c r="BB45" s="155" t="s">
+      <c r="AX45" s="183">
+        <v>46306</v>
+      </c>
+      <c r="AY45" s="136" t="s">
+        <v>171</v>
+      </c>
+      <c r="AZ45" s="138"/>
+      <c r="BA45" s="138"/>
+      <c r="BB45" s="138" t="s">
         <v>212</v>
       </c>
       <c r="BC45" s="149"/>
-      <c r="BE45" s="258"/>
-      <c r="BF45" s="258"/>
-    </row>
-    <row r="46" spans="1:58" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="46" spans="1:55" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A46" s="19"/>
       <c r="B46" s="140"/>
       <c r="C46" s="146" t="s">
@@ -7031,26 +6979,26 @@
       <c r="AS46" s="19"/>
       <c r="AT46" s="181"/>
       <c r="AU46" s="147" t="s">
-        <v>14</v>
-      </c>
-      <c r="AV46" s="149"/>
+        <v>166</v>
+      </c>
+      <c r="AV46" s="149">
+        <v>1</v>
+      </c>
       <c r="AW46" s="141"/>
-      <c r="AX46" s="183">
+      <c r="AX46" s="184">
         <v>46306</v>
       </c>
-      <c r="AY46" s="136" t="s">
-        <v>211</v>
-      </c>
-      <c r="AZ46" s="138"/>
-      <c r="BA46" s="138"/>
-      <c r="BB46" s="138" t="s">
+      <c r="AY46" s="159" t="s">
+        <v>214</v>
+      </c>
+      <c r="AZ46" s="155"/>
+      <c r="BA46" s="155"/>
+      <c r="BB46" s="155" t="s">
         <v>213</v>
       </c>
       <c r="BC46" s="149"/>
-      <c r="BE46" s="258"/>
-      <c r="BF46" s="258"/>
-    </row>
-    <row r="47" spans="1:58" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="47" spans="1:55" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A47" s="19"/>
       <c r="B47" s="140"/>
       <c r="C47" s="146" t="s">
@@ -7120,26 +7068,24 @@
       <c r="AS47" s="19"/>
       <c r="AT47" s="181"/>
       <c r="AU47" s="147" t="s">
-        <v>167</v>
+        <v>14</v>
       </c>
       <c r="AV47" s="149"/>
       <c r="AW47" s="141"/>
-      <c r="AX47" s="184">
-        <v>46306</v>
-      </c>
-      <c r="AY47" s="159" t="s">
-        <v>215</v>
-      </c>
-      <c r="AZ47" s="155"/>
-      <c r="BA47" s="155"/>
-      <c r="BB47" s="155" t="s">
+      <c r="AX47" s="183">
+        <v>46341</v>
+      </c>
+      <c r="AY47" s="136" t="s">
+        <v>212</v>
+      </c>
+      <c r="AZ47" s="138"/>
+      <c r="BA47" s="138"/>
+      <c r="BB47" s="138" t="s">
         <v>214</v>
       </c>
       <c r="BC47" s="192"/>
-      <c r="BE47" s="258"/>
-      <c r="BF47" s="258"/>
-    </row>
-    <row r="48" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="48" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A48" s="19"/>
       <c r="B48" s="140"/>
       <c r="C48" s="146" t="s">
@@ -7209,26 +7155,24 @@
       <c r="AS48" s="19"/>
       <c r="AT48" s="181"/>
       <c r="AU48" s="147" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AV48" s="149"/>
       <c r="AW48" s="141"/>
-      <c r="AX48" s="183">
+      <c r="AX48" s="159">
         <v>46341</v>
       </c>
-      <c r="AY48" s="136" t="s">
-        <v>213</v>
-      </c>
-      <c r="AZ48" s="138"/>
-      <c r="BA48" s="138"/>
-      <c r="BB48" s="138" t="s">
-        <v>215</v>
+      <c r="AY48" s="159" t="s">
+        <v>211</v>
+      </c>
+      <c r="AZ48" s="155"/>
+      <c r="BA48" s="155"/>
+      <c r="BB48" s="155" t="s">
+        <v>171</v>
       </c>
       <c r="BC48" s="149"/>
-      <c r="BE48" s="258"/>
-      <c r="BF48" s="258"/>
-    </row>
-    <row r="49" spans="1:58" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="49" spans="1:57" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A49" s="19"/>
       <c r="B49" s="140"/>
       <c r="C49" s="146" t="s">
@@ -7298,12 +7242,12 @@
       <c r="AS49" s="19"/>
       <c r="AT49" s="181"/>
       <c r="AU49" s="155" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AV49" s="164"/>
       <c r="AW49" s="141"/>
-      <c r="AX49" s="159">
-        <v>46341</v>
+      <c r="AX49" s="184">
+        <v>46348</v>
       </c>
       <c r="AY49" s="159" t="s">
         <v>212</v>
@@ -7314,10 +7258,8 @@
         <v>211</v>
       </c>
       <c r="BC49" s="149"/>
-      <c r="BE49" s="258"/>
-      <c r="BF49" s="258"/>
-    </row>
-    <row r="50" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="50" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A50" s="19"/>
       <c r="B50" s="140"/>
       <c r="C50" s="154" t="s">
@@ -7421,18 +7363,17 @@
         <v>46355</v>
       </c>
       <c r="AY50" s="136" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AZ50" s="138"/>
       <c r="BA50" s="138"/>
       <c r="BB50" s="138" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="BC50" s="149"/>
-      <c r="BE50" s="259"/>
-      <c r="BF50" s="258"/>
-    </row>
-    <row r="51" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="BE50" s="243"/>
+    </row>
+    <row r="51" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A51" s="19"/>
       <c r="B51" s="140"/>
       <c r="C51" s="162"/>
@@ -7522,18 +7463,17 @@
         <v>46355</v>
       </c>
       <c r="AY51" s="159" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AZ51" s="155"/>
       <c r="BA51" s="155"/>
       <c r="BB51" s="155" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="BC51" s="149"/>
-      <c r="BE51" s="259"/>
-      <c r="BF51" s="258"/>
-    </row>
-    <row r="52" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="BE51" s="243"/>
+    </row>
+    <row r="52" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A52" s="19"/>
       <c r="B52" s="156"/>
       <c r="C52" s="157"/>
@@ -7633,18 +7573,17 @@
         <v>46369</v>
       </c>
       <c r="AY52" s="136" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AZ52" s="138"/>
       <c r="BA52" s="138"/>
       <c r="BB52" s="138" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="BC52" s="149"/>
-      <c r="BE52" s="259"/>
-      <c r="BF52" s="258"/>
-    </row>
-    <row r="53" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="BE52" s="243"/>
+    </row>
+    <row r="53" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A53" s="19"/>
       <c r="B53" s="20"/>
       <c r="C53" s="20"/>
@@ -7738,18 +7677,16 @@
         <v>46369</v>
       </c>
       <c r="AY53" s="159" t="s">
-        <v>211</v>
+        <v>171</v>
       </c>
       <c r="AZ53" s="155"/>
       <c r="BA53" s="155"/>
       <c r="BB53" s="155" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="BC53" s="149"/>
-      <c r="BE53" s="258"/>
-      <c r="BF53" s="258"/>
-    </row>
-    <row r="54" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="54" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A54" s="19"/>
       <c r="B54" s="133"/>
       <c r="C54" s="134"/>
@@ -7852,10 +7789,9 @@
       <c r="BA54" s="193"/>
       <c r="BB54" s="193"/>
       <c r="BC54" s="161"/>
-      <c r="BE54" s="259"/>
-      <c r="BF54" s="258"/>
-    </row>
-    <row r="55" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="BE54" s="243"/>
+    </row>
+    <row r="55" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A55" s="19"/>
       <c r="B55" s="140"/>
       <c r="C55" s="162"/>
@@ -7949,10 +7885,9 @@
       <c r="BA55" s="19"/>
       <c r="BB55" s="19"/>
       <c r="BC55" s="65"/>
-      <c r="BE55" s="259"/>
-      <c r="BF55" s="258"/>
-    </row>
-    <row r="56" spans="1:58" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="BE55" s="243"/>
+    </row>
+    <row r="56" spans="1:57" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A56" s="19"/>
       <c r="B56" s="140"/>
       <c r="C56" s="178" t="s">
@@ -8034,10 +7969,9 @@
       <c r="BA56" s="134"/>
       <c r="BB56" s="134"/>
       <c r="BC56" s="139"/>
-      <c r="BE56" s="259"/>
-      <c r="BF56" s="258"/>
-    </row>
-    <row r="57" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="BE56" s="243"/>
+    </row>
+    <row r="57" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A57" s="19"/>
       <c r="B57" s="146"/>
       <c r="C57" s="146" t="s">
@@ -8118,21 +8052,19 @@
       </c>
       <c r="AW57" s="141"/>
       <c r="AX57" s="183">
-        <v>46292</v>
+        <v>46299</v>
       </c>
       <c r="AY57" s="136" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AZ57" s="138"/>
       <c r="BA57" s="138"/>
       <c r="BB57" s="138" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="BC57" s="149"/>
-      <c r="BE57" s="258"/>
-      <c r="BF57" s="258"/>
-    </row>
-    <row r="58" spans="1:58" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="58" spans="1:57" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A58" s="19"/>
       <c r="B58" s="140"/>
       <c r="C58" s="146" t="s">
@@ -8206,26 +8138,24 @@
       <c r="AS58" s="19"/>
       <c r="AT58" s="181"/>
       <c r="AU58" s="137" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AV58" s="138"/>
       <c r="AW58" s="141"/>
-      <c r="AX58" s="184">
-        <v>46292</v>
-      </c>
-      <c r="AY58" s="159" t="s">
-        <v>217</v>
-      </c>
-      <c r="AZ58" s="155"/>
-      <c r="BA58" s="155"/>
-      <c r="BB58" s="155" t="s">
-        <v>204</v>
+      <c r="AX58" s="183">
+        <v>46306</v>
+      </c>
+      <c r="AY58" s="136" t="s">
+        <v>215</v>
+      </c>
+      <c r="AZ58" s="138"/>
+      <c r="BA58" s="138"/>
+      <c r="BB58" s="138" t="s">
+        <v>210</v>
       </c>
       <c r="BC58" s="149"/>
-      <c r="BE58" s="258"/>
-      <c r="BF58" s="258"/>
-    </row>
-    <row r="59" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="59" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A59" s="19"/>
       <c r="B59" s="140"/>
       <c r="C59" s="146" t="s">
@@ -8327,26 +8257,24 @@
       <c r="AS59" s="19"/>
       <c r="AT59" s="181"/>
       <c r="AU59" s="146" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AV59" s="147"/>
       <c r="AW59" s="141"/>
-      <c r="AX59" s="183">
+      <c r="AX59" s="184">
         <v>46306</v>
       </c>
-      <c r="AY59" s="136" t="s">
+      <c r="AY59" s="159" t="s">
+        <v>217</v>
+      </c>
+      <c r="AZ59" s="155"/>
+      <c r="BA59" s="155"/>
+      <c r="BB59" s="155" t="s">
         <v>216</v>
       </c>
-      <c r="AZ59" s="138"/>
-      <c r="BA59" s="138"/>
-      <c r="BB59" s="138" t="s">
-        <v>217</v>
-      </c>
       <c r="BC59" s="149"/>
-      <c r="BE59" s="258"/>
-      <c r="BF59" s="258"/>
-    </row>
-    <row r="60" spans="1:58" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="60" spans="1:57" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A60" s="19"/>
       <c r="B60" s="140"/>
       <c r="C60" s="146" t="s">
@@ -8448,26 +8376,24 @@
       <c r="AS60" s="19"/>
       <c r="AT60" s="181"/>
       <c r="AU60" s="146" t="s">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="AV60" s="147"/>
       <c r="AW60" s="141"/>
       <c r="AX60" s="184">
-        <v>46306</v>
+        <v>46320</v>
       </c>
       <c r="AY60" s="159" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="AZ60" s="155"/>
       <c r="BA60" s="155"/>
       <c r="BB60" s="155" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="BC60" s="149"/>
-      <c r="BE60" s="258"/>
-      <c r="BF60" s="258"/>
-    </row>
-    <row r="61" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="61" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A61" s="19"/>
       <c r="B61" s="140"/>
       <c r="C61" s="154" t="s">
@@ -8569,7 +8495,7 @@
       <c r="AS61" s="19"/>
       <c r="AT61" s="181"/>
       <c r="AU61" s="146" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AV61" s="147"/>
       <c r="AW61" s="141"/>
@@ -8577,18 +8503,16 @@
         <v>46341</v>
       </c>
       <c r="AY61" s="136" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="AZ61" s="138"/>
       <c r="BA61" s="138"/>
       <c r="BB61" s="138" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="BC61" s="149"/>
-      <c r="BE61" s="258"/>
-      <c r="BF61" s="258"/>
-    </row>
-    <row r="62" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="62" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A62" s="19"/>
       <c r="B62" s="146"/>
       <c r="C62" s="162"/>
@@ -8694,18 +8618,16 @@
         <v>46341</v>
       </c>
       <c r="AY62" s="159" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AZ62" s="155"/>
       <c r="BA62" s="155"/>
       <c r="BB62" s="155" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="BC62" s="149"/>
-      <c r="BE62" s="258"/>
-      <c r="BF62" s="258"/>
-    </row>
-    <row r="63" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="63" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A63" s="19"/>
       <c r="B63" s="154"/>
       <c r="C63" s="157"/>
@@ -8805,18 +8727,16 @@
         <v>46355</v>
       </c>
       <c r="AY63" s="136" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AZ63" s="138"/>
       <c r="BA63" s="138"/>
       <c r="BB63" s="138" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="BC63" s="149"/>
-      <c r="BE63" s="258"/>
-      <c r="BF63" s="258"/>
-    </row>
-    <row r="64" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="64" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A64" s="19"/>
       <c r="B64" s="21"/>
       <c r="C64" s="21"/>
@@ -8898,18 +8818,16 @@
         <v>46355</v>
       </c>
       <c r="AY64" s="159" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AZ64" s="155"/>
       <c r="BA64" s="155"/>
       <c r="BB64" s="155" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="BC64" s="149"/>
-      <c r="BE64" s="258"/>
-      <c r="BF64" s="258"/>
-    </row>
-    <row r="65" spans="1:58" x14ac:dyDescent="0.45">
+    </row>
+    <row r="65" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A65" s="19"/>
       <c r="B65" s="133"/>
       <c r="C65" s="134"/>
@@ -8984,18 +8902,16 @@
         <v>46369</v>
       </c>
       <c r="AY65" s="136" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AZ65" s="138"/>
       <c r="BA65" s="138"/>
       <c r="BB65" s="138" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="BC65" s="149"/>
-      <c r="BE65" s="258"/>
-      <c r="BF65" s="258"/>
-    </row>
-    <row r="66" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="66" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A66" s="19"/>
       <c r="B66" s="140"/>
       <c r="C66" s="141"/>
@@ -9067,18 +8983,16 @@
         <v>46369</v>
       </c>
       <c r="AY66" s="159" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AZ66" s="155"/>
       <c r="BA66" s="155"/>
       <c r="BB66" s="155" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="BC66" s="149"/>
-      <c r="BE66" s="258"/>
-      <c r="BF66" s="258"/>
-    </row>
-    <row r="67" spans="1:58" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="67" spans="1:55" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A67" s="19"/>
       <c r="B67" s="140"/>
       <c r="C67" s="178" t="s">
@@ -9147,10 +9061,8 @@
       <c r="BA67" s="162"/>
       <c r="BB67" s="162"/>
       <c r="BC67" s="149"/>
-      <c r="BE67" s="258"/>
-      <c r="BF67" s="258"/>
-    </row>
-    <row r="68" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="68" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A68" s="19"/>
       <c r="B68" s="140"/>
       <c r="C68" s="146" t="s">
@@ -9256,10 +9168,8 @@
       <c r="BA68" s="127"/>
       <c r="BB68" s="127"/>
       <c r="BC68" s="38"/>
-      <c r="BE68" s="258"/>
-      <c r="BF68" s="258"/>
-    </row>
-    <row r="69" spans="1:58" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="69" spans="1:55" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A69" s="19"/>
       <c r="B69" s="140"/>
       <c r="C69" s="146" t="s">
@@ -9365,10 +9275,8 @@
       <c r="BA69" s="162"/>
       <c r="BB69" s="162"/>
       <c r="BC69" s="149"/>
-      <c r="BE69" s="258"/>
-      <c r="BF69" s="258"/>
-    </row>
-    <row r="70" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="70" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A70" s="19"/>
       <c r="B70" s="140"/>
       <c r="C70" s="146" t="s">
@@ -9480,18 +9388,20 @@
         <v>46292</v>
       </c>
       <c r="AY70" s="136" t="s">
-        <v>227</v>
-      </c>
-      <c r="AZ70" s="138"/>
-      <c r="BA70" s="138"/>
+        <v>225</v>
+      </c>
+      <c r="AZ70" s="138">
+        <v>27</v>
+      </c>
+      <c r="BA70" s="138">
+        <v>23</v>
+      </c>
       <c r="BB70" s="138" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="BC70" s="149"/>
-      <c r="BE70" s="258"/>
-      <c r="BF70" s="258"/>
-    </row>
-    <row r="71" spans="1:58" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="71" spans="1:55" ht="15.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A71" s="19"/>
       <c r="B71" s="140"/>
       <c r="C71" s="146" t="s">
@@ -9595,24 +9505,28 @@
       <c r="AU71" s="137" t="s">
         <v>9</v>
       </c>
-      <c r="AV71" s="138"/>
+      <c r="AV71" s="138">
+        <v>5</v>
+      </c>
       <c r="AW71" s="141"/>
       <c r="AX71" s="184">
         <v>46292</v>
       </c>
       <c r="AY71" s="159" t="s">
-        <v>203</v>
-      </c>
-      <c r="AZ71" s="155"/>
-      <c r="BA71" s="155"/>
+        <v>202</v>
+      </c>
+      <c r="AZ71" s="155">
+        <v>64</v>
+      </c>
+      <c r="BA71" s="155">
+        <v>12</v>
+      </c>
       <c r="BB71" s="155" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="BC71" s="192"/>
-      <c r="BE71" s="258"/>
-      <c r="BF71" s="258"/>
-    </row>
-    <row r="72" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="72" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A72" s="19"/>
       <c r="B72" s="140"/>
       <c r="C72" s="154" t="s">
@@ -9720,24 +9634,24 @@
       <c r="AU72" s="146" t="s">
         <v>174</v>
       </c>
-      <c r="AV72" s="147"/>
+      <c r="AV72" s="147">
+        <v>5</v>
+      </c>
       <c r="AW72" s="141"/>
       <c r="AX72" s="183">
         <v>46306</v>
       </c>
       <c r="AY72" s="136" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AZ72" s="138"/>
       <c r="BA72" s="138"/>
       <c r="BB72" s="138" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="BC72" s="149"/>
-      <c r="BE72" s="258"/>
-      <c r="BF72" s="258"/>
-    </row>
-    <row r="73" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="73" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A73" s="19"/>
       <c r="B73" s="140"/>
       <c r="C73" s="162"/>
@@ -9827,26 +9741,26 @@
       <c r="AS73" s="19"/>
       <c r="AT73" s="181"/>
       <c r="AU73" s="146" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV73" s="147"/>
+        <v>173</v>
+      </c>
+      <c r="AV73" s="147">
+        <v>3</v>
+      </c>
       <c r="AW73" s="141"/>
       <c r="AX73" s="184">
         <v>46306</v>
       </c>
       <c r="AY73" s="159" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AZ73" s="155"/>
       <c r="BA73" s="155"/>
       <c r="BB73" s="155" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="BC73" s="149"/>
-      <c r="BE73" s="258"/>
-      <c r="BF73" s="258"/>
-    </row>
-    <row r="74" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="74" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A74" s="19"/>
       <c r="B74" s="156"/>
       <c r="C74" s="157"/>
@@ -9916,9 +9830,11 @@
       <c r="AS74" s="19"/>
       <c r="AT74" s="181"/>
       <c r="AU74" s="146" t="s">
-        <v>175</v>
-      </c>
-      <c r="AV74" s="147"/>
+        <v>2</v>
+      </c>
+      <c r="AV74" s="147">
+        <v>1</v>
+      </c>
       <c r="AW74" s="141" t="s">
         <v>3</v>
       </c>
@@ -9926,18 +9842,16 @@
         <v>46341</v>
       </c>
       <c r="AY74" s="136" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AZ74" s="138"/>
       <c r="BA74" s="138"/>
       <c r="BB74" s="138" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="BC74" s="149"/>
-      <c r="BE74" s="258"/>
-      <c r="BF74" s="258"/>
-    </row>
-    <row r="75" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="75" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A75" s="19"/>
       <c r="B75" s="21"/>
       <c r="C75" s="20"/>
@@ -9997,7 +9911,7 @@
       <c r="AS75" s="19"/>
       <c r="AT75" s="181"/>
       <c r="AU75" s="154" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="AV75" s="155"/>
       <c r="AW75" s="141"/>
@@ -10005,18 +9919,16 @@
         <v>46341</v>
       </c>
       <c r="AY75" s="159" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AZ75" s="155"/>
       <c r="BA75" s="155"/>
       <c r="BB75" s="155" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="BC75" s="149"/>
-      <c r="BE75" s="258"/>
-      <c r="BF75" s="258"/>
-    </row>
-    <row r="76" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="76" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A76" s="19"/>
       <c r="B76" s="21"/>
       <c r="C76" s="20"/>
@@ -10078,18 +9990,16 @@
         <v>46355</v>
       </c>
       <c r="AY76" s="136" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AZ76" s="138"/>
       <c r="BA76" s="138"/>
       <c r="BB76" s="138" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="BC76" s="149"/>
-      <c r="BE76" s="258"/>
-      <c r="BF76" s="258"/>
-    </row>
-    <row r="77" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="77" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A77" s="19"/>
       <c r="B77" s="21"/>
       <c r="C77" s="20"/>
@@ -10179,18 +10089,16 @@
         <v>46355</v>
       </c>
       <c r="AY77" s="159" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AZ77" s="155"/>
       <c r="BA77" s="155"/>
       <c r="BB77" s="155" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="BC77" s="149"/>
-      <c r="BE77" s="258"/>
-      <c r="BF77" s="258"/>
-    </row>
-    <row r="78" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="78" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A78" s="19"/>
       <c r="B78" s="21"/>
       <c r="C78" s="20"/>
@@ -10270,18 +10178,16 @@
         <v>46369</v>
       </c>
       <c r="AY78" s="136" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AZ78" s="138"/>
       <c r="BA78" s="138"/>
       <c r="BB78" s="138" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="BC78" s="149"/>
-      <c r="BE78" s="258"/>
-      <c r="BF78" s="258"/>
-    </row>
-    <row r="79" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="79" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A79" s="19"/>
       <c r="B79" s="21"/>
       <c r="C79" s="20"/>
@@ -10371,18 +10277,16 @@
         <v>46369</v>
       </c>
       <c r="AY79" s="159" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AZ79" s="155"/>
       <c r="BA79" s="155"/>
       <c r="BB79" s="155" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="BC79" s="149"/>
-      <c r="BE79" s="258"/>
-      <c r="BF79" s="258"/>
-    </row>
-    <row r="80" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="80" spans="1:55" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A80" s="19"/>
       <c r="B80" s="21"/>
       <c r="C80" s="20"/>
@@ -10474,10 +10378,8 @@
       <c r="BA80" s="162"/>
       <c r="BB80" s="162"/>
       <c r="BC80" s="149"/>
-      <c r="BE80" s="258"/>
-      <c r="BF80" s="258"/>
-    </row>
-    <row r="81" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="81" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A81" s="19"/>
       <c r="B81" s="21"/>
       <c r="C81" s="20"/>
@@ -10573,10 +10475,8 @@
       <c r="BA81" s="19"/>
       <c r="BB81" s="19"/>
       <c r="BC81" s="65"/>
-      <c r="BE81" s="258"/>
-      <c r="BF81" s="258"/>
-    </row>
-    <row r="82" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="82" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A82" s="19"/>
       <c r="B82" s="21"/>
       <c r="C82" s="20"/>
@@ -10664,10 +10564,8 @@
       <c r="BA82" s="162"/>
       <c r="BB82" s="162"/>
       <c r="BC82" s="149"/>
-      <c r="BE82" s="258"/>
-      <c r="BF82" s="258"/>
-    </row>
-    <row r="83" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="83" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A83" s="19"/>
       <c r="B83" s="21"/>
       <c r="C83" s="20"/>
@@ -10733,22 +10631,25 @@
         <v>4</v>
       </c>
       <c r="AW83" s="141"/>
-      <c r="AX83" s="183">
-        <v>46292</v>
+      <c r="AX83" s="136" t="s">
+        <v>268</v>
       </c>
       <c r="AY83" s="136" t="s">
-        <v>205</v>
-      </c>
-      <c r="AZ83" s="138"/>
-      <c r="BA83" s="138"/>
+        <v>204</v>
+      </c>
+      <c r="AZ83" s="138">
+        <v>30</v>
+      </c>
+      <c r="BA83" s="138">
+        <v>0</v>
+      </c>
       <c r="BB83" s="138" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="BC83" s="149"/>
-      <c r="BE83" s="260"/>
-      <c r="BF83" s="258"/>
-    </row>
-    <row r="84" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="BE83" s="244"/>
+    </row>
+    <row r="84" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A84" s="19"/>
       <c r="B84" s="21"/>
       <c r="C84" s="20"/>
@@ -10810,24 +10711,28 @@
       <c r="AU84" s="137" t="s">
         <v>176</v>
       </c>
-      <c r="AV84" s="138"/>
+      <c r="AV84" s="138">
+        <v>5</v>
+      </c>
       <c r="AW84" s="141"/>
       <c r="AX84" s="184">
         <v>46292</v>
       </c>
       <c r="AY84" s="159" t="s">
-        <v>229</v>
-      </c>
-      <c r="AZ84" s="155"/>
-      <c r="BA84" s="155"/>
+        <v>227</v>
+      </c>
+      <c r="AZ84" s="155">
+        <v>36</v>
+      </c>
+      <c r="BA84" s="155">
+        <v>21</v>
+      </c>
       <c r="BB84" s="155" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="BC84" s="149"/>
-      <c r="BE84" s="258"/>
-      <c r="BF84" s="258"/>
-    </row>
-    <row r="85" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="85" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A85" s="19"/>
       <c r="B85" s="21"/>
       <c r="C85" s="20"/>
@@ -10887,26 +10792,26 @@
       <c r="AS85" s="19"/>
       <c r="AT85" s="181"/>
       <c r="AU85" s="146" t="s">
-        <v>177</v>
-      </c>
-      <c r="AV85" s="147"/>
+        <v>1</v>
+      </c>
+      <c r="AV85" s="147">
+        <v>5</v>
+      </c>
       <c r="AW85" s="141"/>
-      <c r="AX85" s="183">
+      <c r="AX85" s="184">
         <v>46306</v>
       </c>
-      <c r="AY85" s="136" t="s">
-        <v>202</v>
-      </c>
-      <c r="AZ85" s="138"/>
-      <c r="BA85" s="138"/>
-      <c r="BB85" s="138" t="s">
-        <v>229</v>
+      <c r="AY85" s="159" t="s">
+        <v>206</v>
+      </c>
+      <c r="AZ85" s="155"/>
+      <c r="BA85" s="155"/>
+      <c r="BB85" s="155" t="s">
+        <v>204</v>
       </c>
       <c r="BC85" s="149"/>
-      <c r="BE85" s="258"/>
-      <c r="BF85" s="258"/>
-    </row>
-    <row r="86" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="86" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A86" s="19"/>
       <c r="B86" s="21"/>
       <c r="C86" s="20"/>
@@ -10994,26 +10899,26 @@
       <c r="AS86" s="19"/>
       <c r="AT86" s="181"/>
       <c r="AU86" s="146" t="s">
-        <v>8</v>
-      </c>
-      <c r="AV86" s="147"/>
+        <v>175</v>
+      </c>
+      <c r="AV86" s="147">
+        <v>1</v>
+      </c>
       <c r="AW86" s="141"/>
-      <c r="AX86" s="184">
-        <v>46306</v>
-      </c>
-      <c r="AY86" s="159" t="s">
-        <v>207</v>
-      </c>
-      <c r="AZ86" s="155"/>
-      <c r="BA86" s="155"/>
-      <c r="BB86" s="155" t="s">
-        <v>205</v>
+      <c r="AX86" s="183">
+        <v>46341</v>
+      </c>
+      <c r="AY86" s="136" t="s">
+        <v>227</v>
+      </c>
+      <c r="AZ86" s="138"/>
+      <c r="BA86" s="138"/>
+      <c r="BB86" s="138" t="s">
+        <v>206</v>
       </c>
       <c r="BC86" s="149"/>
-      <c r="BE86" s="258"/>
-      <c r="BF86" s="258"/>
-    </row>
-    <row r="87" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="87" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A87" s="19"/>
       <c r="B87" s="21"/>
       <c r="C87" s="20"/>
@@ -11099,24 +11004,24 @@
       <c r="AU87" s="146" t="s">
         <v>93</v>
       </c>
-      <c r="AV87" s="147"/>
+      <c r="AV87" s="147">
+        <v>1</v>
+      </c>
       <c r="AW87" s="141"/>
-      <c r="AX87" s="183">
-        <v>46341</v>
-      </c>
-      <c r="AY87" s="136" t="s">
-        <v>229</v>
-      </c>
-      <c r="AZ87" s="138"/>
-      <c r="BA87" s="138"/>
-      <c r="BB87" s="138" t="s">
+      <c r="AX87" s="159">
+        <v>46334</v>
+      </c>
+      <c r="AY87" s="159" t="s">
         <v>207</v>
       </c>
+      <c r="AZ87" s="155"/>
+      <c r="BA87" s="155"/>
+      <c r="BB87" s="155" t="s">
+        <v>201</v>
+      </c>
       <c r="BC87" s="149"/>
-      <c r="BE87" s="258"/>
-      <c r="BF87" s="258"/>
-    </row>
-    <row r="88" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="88" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A88" s="19"/>
       <c r="B88" s="21"/>
       <c r="C88" s="20"/>
@@ -11200,24 +11105,24 @@
       <c r="AS88" s="19"/>
       <c r="AT88" s="181"/>
       <c r="AU88" s="154" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AV88" s="155"/>
       <c r="AW88" s="141"/>
-      <c r="AX88" s="159">
-        <v>46341</v>
-      </c>
-      <c r="AY88" s="159" t="s">
-        <v>208</v>
-      </c>
-      <c r="AZ88" s="155"/>
-      <c r="BA88" s="155"/>
-      <c r="BB88" s="155" t="s">
-        <v>202</v>
+      <c r="AX88" s="183">
+        <v>46348</v>
+      </c>
+      <c r="AY88" s="136" t="s">
+        <v>201</v>
+      </c>
+      <c r="AZ88" s="138"/>
+      <c r="BA88" s="138"/>
+      <c r="BB88" s="138" t="s">
+        <v>227</v>
       </c>
       <c r="BC88" s="149"/>
     </row>
-    <row r="89" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A89" s="19"/>
       <c r="B89" s="21"/>
       <c r="C89" s="20"/>
@@ -11277,16 +11182,16 @@
         <v>46355</v>
       </c>
       <c r="AY89" s="136" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AZ89" s="138"/>
       <c r="BA89" s="138"/>
       <c r="BB89" s="138" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="BC89" s="149"/>
     </row>
-    <row r="90" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="O90" s="2"/>
       <c r="P90" s="2"/>
       <c r="R90" s="5"/>
@@ -11321,16 +11226,16 @@
         <v>46355</v>
       </c>
       <c r="AY90" s="159" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AZ90" s="155"/>
       <c r="BA90" s="155"/>
       <c r="BB90" s="155" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="BC90" s="149"/>
     </row>
-    <row r="91" spans="1:58" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:57" x14ac:dyDescent="0.45">
       <c r="R91" s="5"/>
       <c r="W91" s="19"/>
       <c r="X91" s="41"/>
@@ -11365,16 +11270,16 @@
         <v>46369</v>
       </c>
       <c r="AY91" s="136" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AZ91" s="138"/>
       <c r="BA91" s="138"/>
       <c r="BB91" s="138" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BC91" s="149"/>
     </row>
-    <row r="92" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="R92" s="5"/>
       <c r="AC92" s="5"/>
       <c r="AD92" s="1"/>
@@ -11394,16 +11299,16 @@
         <v>46369</v>
       </c>
       <c r="AY92" s="159" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AZ92" s="155"/>
       <c r="BA92" s="155"/>
       <c r="BB92" s="155" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="BC92" s="149"/>
     </row>
-    <row r="93" spans="1:58" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:57" x14ac:dyDescent="0.45">
       <c r="R93" s="5"/>
       <c r="AC93" s="5"/>
       <c r="AD93" s="1"/>
@@ -11426,7 +11331,7 @@
       <c r="BB93" s="162"/>
       <c r="BC93" s="149"/>
     </row>
-    <row r="94" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="R94" s="5"/>
       <c r="AC94" s="5"/>
       <c r="AD94" s="1"/>
@@ -11449,7 +11354,7 @@
       <c r="BB94" s="225"/>
       <c r="BC94" s="226"/>
     </row>
-    <row r="95" spans="1:58" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:57" x14ac:dyDescent="0.45">
       <c r="R95" s="5"/>
       <c r="AC95" s="5"/>
       <c r="AD95" s="1"/>
@@ -11471,7 +11376,7 @@
       <c r="BB95" s="1"/>
       <c r="BC95" s="1"/>
     </row>
-    <row r="96" spans="1:58" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:57" x14ac:dyDescent="0.45">
       <c r="R96" s="5"/>
       <c r="AC96" s="5"/>
       <c r="AD96" s="1"/>
@@ -12067,8 +11972,8 @@
       <c r="AV146" s="3"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AJ78:AK81">
-    <sortCondition descending="1" ref="AK78:AK81"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AU84:AV88">
+    <sortCondition descending="1" ref="AV84:AV88"/>
   </sortState>
   <mergeCells count="15">
     <mergeCell ref="AT2:BC2"/>
@@ -12101,19 +12006,20 @@
   <dimension ref="A1:U117"/>
   <sheetFormatPr defaultRowHeight="14.65" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="18.265625" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="7" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="18.19921875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="6.9296875" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="9.06640625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="9.06640625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="19.53125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1328125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="6.9296875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="18.3984375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11.1328125" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="9.06640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.86328125" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="11.33203125" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="26.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.59765625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="11.1328125" hidden="1" customWidth="1"/>
+    <col min="12" max="13" width="9.06640625" customWidth="1"/>
+    <col min="14" max="14" width="21.06640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.06640625" style="2"/>
     <col min="17" max="17" width="12.46484375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="54.265625" style="1" bestFit="1" customWidth="1"/>
@@ -12152,22 +12058,22 @@
         <v>159</v>
       </c>
       <c r="J2" s="229" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K2" s="228" t="s">
         <v>160</v>
       </c>
-      <c r="M2" s="243" t="s">
-        <v>200</v>
-      </c>
-      <c r="N2" s="248"/>
-      <c r="O2" s="248"/>
-      <c r="P2" s="248"/>
-      <c r="Q2" s="248"/>
-      <c r="R2" s="248"/>
-      <c r="S2" s="248"/>
-      <c r="T2" s="248"/>
-      <c r="U2" s="249"/>
+      <c r="M2" s="245" t="s">
+        <v>199</v>
+      </c>
+      <c r="N2" s="250"/>
+      <c r="O2" s="250"/>
+      <c r="P2" s="250"/>
+      <c r="Q2" s="250"/>
+      <c r="R2" s="250"/>
+      <c r="S2" s="250"/>
+      <c r="T2" s="250"/>
+      <c r="U2" s="251"/>
     </row>
     <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="213" t="s">
@@ -12195,20 +12101,20 @@
         <v>160</v>
       </c>
       <c r="M3" s="115"/>
-      <c r="N3" s="246" t="s">
+      <c r="N3" s="248" t="s">
         <v>58</v>
       </c>
-      <c r="O3" s="246"/>
+      <c r="O3" s="248"/>
       <c r="P3" s="114"/>
       <c r="Q3" s="113" t="s">
         <v>57</v>
       </c>
-      <c r="R3" s="246" t="s">
+      <c r="R3" s="248" t="s">
         <v>56</v>
       </c>
-      <c r="S3" s="246"/>
-      <c r="T3" s="246"/>
-      <c r="U3" s="247"/>
+      <c r="S3" s="248"/>
+      <c r="T3" s="248"/>
+      <c r="U3" s="249"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A4" s="212" t="s">
@@ -12218,19 +12124,19 @@
         <v>159</v>
       </c>
       <c r="D4" s="229" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E4" s="228" t="s">
         <v>160</v>
       </c>
       <c r="G4" s="229" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H4" s="228" t="s">
         <v>159</v>
       </c>
       <c r="J4" s="229" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K4" s="228" t="s">
         <v>160</v>
@@ -12243,17 +12149,21 @@
         <v>46292</v>
       </c>
       <c r="R4" s="92" t="s">
-        <v>235</v>
-      </c>
-      <c r="S4" s="103"/>
-      <c r="T4" s="92"/>
+        <v>233</v>
+      </c>
+      <c r="S4" s="103">
+        <v>30</v>
+      </c>
+      <c r="T4" s="92">
+        <v>0</v>
+      </c>
       <c r="U4" s="92" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A5" s="229" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B5" s="228" t="s">
         <v>159</v>
@@ -12271,7 +12181,7 @@
         <v>160</v>
       </c>
       <c r="J5" s="229" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K5" s="228" t="s">
         <v>160</v>
@@ -12284,12 +12194,16 @@
         <v>46292</v>
       </c>
       <c r="R5" s="103" t="s">
-        <v>234</v>
-      </c>
-      <c r="S5" s="103"/>
-      <c r="T5" s="92"/>
+        <v>232</v>
+      </c>
+      <c r="S5" s="103">
+        <v>25</v>
+      </c>
+      <c r="T5" s="92">
+        <v>35</v>
+      </c>
       <c r="U5" s="92" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -12306,13 +12220,13 @@
         <v>159</v>
       </c>
       <c r="G6" s="229" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H6" s="228" t="s">
         <v>160</v>
       </c>
       <c r="J6" s="229" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K6" s="228" t="s">
         <v>160</v>
@@ -12325,17 +12239,21 @@
         <v>46292</v>
       </c>
       <c r="R6" s="88" t="s">
-        <v>233</v>
-      </c>
-      <c r="S6" s="105"/>
-      <c r="T6" s="88"/>
+        <v>231</v>
+      </c>
+      <c r="S6" s="105">
+        <v>0</v>
+      </c>
+      <c r="T6" s="88">
+        <v>30</v>
+      </c>
       <c r="U6" s="88" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="229" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B7" s="228" t="s">
         <v>159</v>
@@ -12347,13 +12265,13 @@
         <v>159</v>
       </c>
       <c r="G7" s="229" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H7" s="228" t="s">
         <v>160</v>
       </c>
       <c r="J7" s="229" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K7" s="228" t="s">
         <v>160</v>
@@ -12366,12 +12284,12 @@
         <v>46306</v>
       </c>
       <c r="R7" s="92" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="S7" s="103"/>
       <c r="T7" s="92"/>
       <c r="U7" s="92" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -12387,12 +12305,12 @@
         <v>46306</v>
       </c>
       <c r="R8" s="103" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="S8" s="103"/>
       <c r="T8" s="92"/>
       <c r="U8" s="92" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -12400,37 +12318,41 @@
       <c r="N9" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="O9" s="44"/>
+      <c r="O9" s="44">
+        <v>5</v>
+      </c>
       <c r="P9" s="30"/>
       <c r="Q9" s="108">
         <v>46306</v>
       </c>
       <c r="R9" s="88" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="S9" s="105"/>
       <c r="T9" s="88"/>
       <c r="U9" s="88" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.45">
       <c r="M10" s="76"/>
       <c r="N10" s="34" t="s">
-        <v>147</v>
-      </c>
-      <c r="O10" s="34"/>
+        <v>35</v>
+      </c>
+      <c r="O10" s="34">
+        <v>5</v>
+      </c>
       <c r="P10" s="30"/>
       <c r="Q10" s="109">
         <v>46341</v>
       </c>
       <c r="R10" s="92" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="S10" s="103"/>
       <c r="T10" s="92"/>
       <c r="U10" s="92" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.45">
@@ -12447,32 +12369,34 @@
         <v>159</v>
       </c>
       <c r="G11" s="229" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H11" s="228" t="s">
         <v>161</v>
       </c>
       <c r="M11" s="76"/>
       <c r="N11" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="O11" s="34"/>
+        <v>134</v>
+      </c>
+      <c r="O11" s="34">
+        <v>5</v>
+      </c>
       <c r="P11" s="30"/>
       <c r="Q11" s="109">
         <v>46341</v>
       </c>
       <c r="R11" s="103" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="S11" s="103"/>
       <c r="T11" s="92"/>
       <c r="U11" s="92" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="229" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B12" s="228" t="s">
         <v>161</v>
@@ -12491,20 +12415,22 @@
       </c>
       <c r="M12" s="76"/>
       <c r="N12" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="O12" s="34"/>
+        <v>147</v>
+      </c>
+      <c r="O12" s="34">
+        <v>3</v>
+      </c>
       <c r="P12" s="30"/>
       <c r="Q12" s="108">
         <v>46341</v>
       </c>
       <c r="R12" s="88" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="S12" s="105"/>
       <c r="T12" s="88"/>
       <c r="U12" s="88" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.45">
@@ -12515,70 +12441,74 @@
         <v>161</v>
       </c>
       <c r="D13" s="229" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E13" s="228" t="s">
         <v>159</v>
       </c>
       <c r="G13" s="229" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H13" s="228" t="s">
         <v>161</v>
       </c>
       <c r="M13" s="76"/>
       <c r="N13" s="34" t="s">
-        <v>134</v>
-      </c>
-      <c r="O13" s="34"/>
+        <v>177</v>
+      </c>
+      <c r="O13" s="34">
+        <v>1</v>
+      </c>
       <c r="P13" s="30"/>
       <c r="Q13" s="109">
         <v>46355</v>
       </c>
       <c r="R13" s="92" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="S13" s="103"/>
       <c r="T13" s="92"/>
       <c r="U13" s="92" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="229" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B14" s="228" t="s">
         <v>161</v>
       </c>
       <c r="D14" s="229" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E14" s="228" t="s">
         <v>159</v>
       </c>
       <c r="G14" s="229" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H14" s="228" t="s">
         <v>161</v>
       </c>
       <c r="M14" s="76"/>
       <c r="N14" s="36" t="s">
-        <v>197</v>
-      </c>
-      <c r="O14" s="36"/>
+        <v>196</v>
+      </c>
+      <c r="O14" s="36">
+        <v>1</v>
+      </c>
       <c r="P14" s="30"/>
       <c r="Q14" s="109">
         <v>46355</v>
       </c>
       <c r="R14" s="103" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="S14" s="103"/>
       <c r="T14" s="92"/>
       <c r="U14" s="92" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -12589,13 +12519,13 @@
         <v>161</v>
       </c>
       <c r="D15" s="229" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E15" s="228" t="s">
         <v>159</v>
       </c>
       <c r="G15" s="229" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H15" s="228" t="s">
         <v>161</v>
@@ -12608,17 +12538,17 @@
         <v>46355</v>
       </c>
       <c r="R15" s="88" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="S15" s="105"/>
       <c r="T15" s="88"/>
       <c r="U15" s="88" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A16" s="229" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B16" s="228" t="s">
         <v>161</v>
@@ -12630,7 +12560,7 @@
         <v>159</v>
       </c>
       <c r="G16" s="229" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H16" s="228" t="s">
         <v>161</v>
@@ -12643,12 +12573,12 @@
         <v>46369</v>
       </c>
       <c r="R16" s="96" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="S16" s="104"/>
       <c r="T16" s="96"/>
       <c r="U16" s="95" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17" spans="6:21" x14ac:dyDescent="0.45">
@@ -12660,12 +12590,12 @@
         <v>46369</v>
       </c>
       <c r="R17" s="92" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="S17" s="103"/>
       <c r="T17" s="92"/>
       <c r="U17" s="91" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" spans="6:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -12677,12 +12607,12 @@
         <v>46369</v>
       </c>
       <c r="R18" s="108" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="S18" s="103"/>
       <c r="T18" s="92"/>
       <c r="U18" s="107" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="6:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -12705,12 +12635,16 @@
         <v>46292</v>
       </c>
       <c r="R20" s="92" t="s">
-        <v>236</v>
-      </c>
-      <c r="S20" s="103"/>
-      <c r="T20" s="92"/>
+        <v>234</v>
+      </c>
+      <c r="S20" s="103">
+        <v>30</v>
+      </c>
+      <c r="T20" s="92">
+        <v>0</v>
+      </c>
       <c r="U20" s="92" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21" spans="6:21" x14ac:dyDescent="0.45">
@@ -12725,12 +12659,16 @@
         <v>46292</v>
       </c>
       <c r="R21" s="103" t="s">
-        <v>237</v>
-      </c>
-      <c r="S21" s="103"/>
-      <c r="T21" s="92"/>
+        <v>235</v>
+      </c>
+      <c r="S21" s="103">
+        <v>25</v>
+      </c>
+      <c r="T21" s="92">
+        <v>20</v>
+      </c>
       <c r="U21" s="92" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22" spans="6:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -12742,12 +12680,16 @@
         <v>46292</v>
       </c>
       <c r="R22" s="88" t="s">
-        <v>238</v>
-      </c>
-      <c r="S22" s="105"/>
-      <c r="T22" s="88"/>
+        <v>236</v>
+      </c>
+      <c r="S22" s="105">
+        <v>0</v>
+      </c>
+      <c r="T22" s="88">
+        <v>15</v>
+      </c>
       <c r="U22" s="88" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="6:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -12759,12 +12701,12 @@
         <v>46306</v>
       </c>
       <c r="R23" s="92" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="S23" s="103"/>
       <c r="T23" s="92"/>
       <c r="U23" s="92" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="24" spans="6:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -12780,50 +12722,54 @@
         <v>46306</v>
       </c>
       <c r="R24" s="103" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="S24" s="103"/>
       <c r="T24" s="92"/>
       <c r="U24" s="92" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="25" spans="6:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="M25" s="76"/>
       <c r="N25" s="44" t="s">
-        <v>141</v>
-      </c>
-      <c r="O25" s="44"/>
+        <v>181</v>
+      </c>
+      <c r="O25" s="44">
+        <v>5</v>
+      </c>
       <c r="P25" s="30"/>
       <c r="Q25" s="108">
         <v>46306</v>
       </c>
       <c r="R25" s="88" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="S25" s="105"/>
       <c r="T25" s="88"/>
       <c r="U25" s="88" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="26" spans="6:21" x14ac:dyDescent="0.45">
       <c r="M26" s="76"/>
       <c r="N26" s="34" t="s">
-        <v>182</v>
-      </c>
-      <c r="O26" s="34"/>
+        <v>143</v>
+      </c>
+      <c r="O26" s="34">
+        <v>5</v>
+      </c>
       <c r="P26" s="30"/>
       <c r="Q26" s="109">
         <v>46341</v>
       </c>
       <c r="R26" s="92" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="S26" s="103"/>
       <c r="T26" s="92"/>
       <c r="U26" s="92" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="27" spans="6:21" x14ac:dyDescent="0.45">
@@ -12831,75 +12777,83 @@
       <c r="N27" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="O27" s="34"/>
+      <c r="O27" s="34">
+        <v>4</v>
+      </c>
       <c r="P27" s="30"/>
       <c r="Q27" s="109">
         <v>46341</v>
       </c>
       <c r="R27" s="103" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S27" s="103"/>
       <c r="T27" s="92"/>
       <c r="U27" s="92" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="28" spans="6:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="M28" s="76"/>
       <c r="N28" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="O28" s="34"/>
+        <v>193</v>
+      </c>
+      <c r="O28" s="34">
+        <v>3</v>
+      </c>
       <c r="P28" s="30"/>
       <c r="Q28" s="108">
         <v>46341</v>
       </c>
       <c r="R28" s="88" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="S28" s="105"/>
       <c r="T28" s="88"/>
       <c r="U28" s="88" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="29" spans="6:21" x14ac:dyDescent="0.45">
       <c r="M29" s="76"/>
       <c r="N29" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="O29" s="34"/>
+        <v>141</v>
+      </c>
+      <c r="O29" s="34">
+        <v>1</v>
+      </c>
       <c r="P29" s="30"/>
       <c r="Q29" s="109">
         <v>46355</v>
       </c>
       <c r="R29" s="92" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="S29" s="103"/>
       <c r="T29" s="92"/>
       <c r="U29" s="92" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="30" spans="6:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="M30" s="76"/>
       <c r="N30" s="36" t="s">
-        <v>194</v>
-      </c>
-      <c r="O30" s="36"/>
+        <v>102</v>
+      </c>
+      <c r="O30" s="36">
+        <v>1</v>
+      </c>
       <c r="P30" s="30"/>
       <c r="Q30" s="109">
         <v>46355</v>
       </c>
       <c r="R30" s="103" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="S30" s="103"/>
       <c r="T30" s="92"/>
       <c r="U30" s="92" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31" spans="6:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -12911,12 +12865,12 @@
         <v>46355</v>
       </c>
       <c r="R31" s="88" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="S31" s="105"/>
       <c r="T31" s="88"/>
       <c r="U31" s="88" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="32" spans="6:21" x14ac:dyDescent="0.45">
@@ -12928,12 +12882,12 @@
         <v>46369</v>
       </c>
       <c r="R32" s="96" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S32" s="104"/>
       <c r="T32" s="96"/>
       <c r="U32" s="95" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="33" spans="13:21" x14ac:dyDescent="0.45">
@@ -12945,12 +12899,12 @@
         <v>46369</v>
       </c>
       <c r="R33" s="92" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="S33" s="103"/>
       <c r="T33" s="92"/>
       <c r="U33" s="91" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="34" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -12962,12 +12916,12 @@
         <v>46369</v>
       </c>
       <c r="R34" s="108" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="S34" s="103"/>
       <c r="T34" s="92"/>
       <c r="U34" s="107" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="35" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -12990,12 +12944,16 @@
         <v>46292</v>
       </c>
       <c r="R36" s="92" t="s">
-        <v>242</v>
-      </c>
-      <c r="S36" s="103"/>
-      <c r="T36" s="92"/>
+        <v>240</v>
+      </c>
+      <c r="S36" s="103">
+        <v>35</v>
+      </c>
+      <c r="T36" s="92">
+        <v>20</v>
+      </c>
       <c r="U36" s="92" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="37" spans="13:21" x14ac:dyDescent="0.45">
@@ -13007,12 +12965,16 @@
         <v>46292</v>
       </c>
       <c r="R37" s="103" t="s">
-        <v>243</v>
-      </c>
-      <c r="S37" s="103"/>
-      <c r="T37" s="92"/>
+        <v>241</v>
+      </c>
+      <c r="S37" s="103">
+        <v>30</v>
+      </c>
+      <c r="T37" s="92">
+        <v>0</v>
+      </c>
       <c r="U37" s="92" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="38" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -13024,12 +12986,12 @@
         <v>46292</v>
       </c>
       <c r="R38" s="88" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="S38" s="105"/>
       <c r="T38" s="88"/>
       <c r="U38" s="88" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="39" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -13041,12 +13003,12 @@
         <v>46306</v>
       </c>
       <c r="R39" s="92" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="S39" s="103"/>
       <c r="T39" s="92"/>
       <c r="U39" s="92" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="40" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -13062,94 +13024,102 @@
         <v>46306</v>
       </c>
       <c r="R40" s="103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="S40" s="103"/>
       <c r="T40" s="92"/>
       <c r="U40" s="92" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="41" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="M41" s="76"/>
       <c r="N41" s="44" t="s">
-        <v>135</v>
-      </c>
-      <c r="O41" s="44"/>
+        <v>184</v>
+      </c>
+      <c r="O41" s="44">
+        <v>5</v>
+      </c>
       <c r="P41" s="30"/>
       <c r="Q41" s="108">
         <v>46306</v>
       </c>
       <c r="R41" s="88" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="S41" s="105"/>
       <c r="T41" s="88"/>
       <c r="U41" s="88" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="42" spans="13:21" x14ac:dyDescent="0.45">
       <c r="M42" s="76"/>
       <c r="N42" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="O42" s="34"/>
+        <v>158</v>
+      </c>
+      <c r="O42" s="34">
+        <v>5</v>
+      </c>
       <c r="P42" s="30"/>
       <c r="Q42" s="109">
         <v>46341</v>
       </c>
       <c r="R42" s="92" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="S42" s="103"/>
       <c r="T42" s="92"/>
       <c r="U42" s="92" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="43" spans="13:21" x14ac:dyDescent="0.45">
       <c r="M43" s="76"/>
       <c r="N43" s="34" t="s">
-        <v>185</v>
-      </c>
-      <c r="O43" s="34"/>
+        <v>139</v>
+      </c>
+      <c r="O43" s="34">
+        <v>2</v>
+      </c>
       <c r="P43" s="30"/>
       <c r="Q43" s="109">
         <v>46341</v>
       </c>
       <c r="R43" s="103" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="S43" s="103"/>
       <c r="T43" s="92"/>
       <c r="U43" s="92" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="44" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="M44" s="76"/>
       <c r="N44" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="O44" s="34"/>
+        <v>135</v>
+      </c>
+      <c r="O44" s="34">
+        <v>1</v>
+      </c>
       <c r="P44" s="30"/>
       <c r="Q44" s="108">
         <v>46341</v>
       </c>
       <c r="R44" s="88" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="S44" s="105"/>
       <c r="T44" s="88"/>
       <c r="U44" s="88" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="45" spans="13:21" x14ac:dyDescent="0.45">
       <c r="M45" s="76"/>
       <c r="N45" s="34" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="O45" s="34"/>
       <c r="P45" s="30"/>
@@ -13157,12 +13127,12 @@
         <v>46355</v>
       </c>
       <c r="R45" s="92" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="S45" s="103"/>
       <c r="T45" s="92"/>
       <c r="U45" s="92" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="46" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -13176,12 +13146,12 @@
         <v>46355</v>
       </c>
       <c r="R46" s="103" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="S46" s="103"/>
       <c r="T46" s="92"/>
       <c r="U46" s="92" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="47" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -13193,12 +13163,12 @@
         <v>46355</v>
       </c>
       <c r="R47" s="88" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="S47" s="105"/>
       <c r="T47" s="88"/>
       <c r="U47" s="88" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="48" spans="13:21" x14ac:dyDescent="0.45">
@@ -13210,12 +13180,12 @@
         <v>46369</v>
       </c>
       <c r="R48" s="96" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="S48" s="104"/>
       <c r="T48" s="96"/>
       <c r="U48" s="95" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="49" spans="13:21" x14ac:dyDescent="0.45">
@@ -13227,12 +13197,12 @@
         <v>46369</v>
       </c>
       <c r="R49" s="92" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="S49" s="103"/>
       <c r="T49" s="92"/>
       <c r="U49" s="91" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="50" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -13244,12 +13214,12 @@
         <v>46369</v>
       </c>
       <c r="R50" s="108" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="S50" s="103"/>
       <c r="T50" s="92"/>
       <c r="U50" s="107" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="51" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -13272,12 +13242,16 @@
         <v>46292</v>
       </c>
       <c r="R52" s="92" t="s">
-        <v>248</v>
-      </c>
-      <c r="S52" s="103"/>
-      <c r="T52" s="92"/>
+        <v>246</v>
+      </c>
+      <c r="S52" s="103">
+        <v>35</v>
+      </c>
+      <c r="T52" s="92">
+        <v>25</v>
+      </c>
       <c r="U52" s="92" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="53" spans="13:21" x14ac:dyDescent="0.45">
@@ -13289,12 +13263,16 @@
         <v>46292</v>
       </c>
       <c r="R53" s="103" t="s">
-        <v>249</v>
-      </c>
-      <c r="S53" s="103"/>
-      <c r="T53" s="92"/>
+        <v>247</v>
+      </c>
+      <c r="S53" s="103">
+        <v>30</v>
+      </c>
+      <c r="T53" s="92">
+        <v>15</v>
+      </c>
       <c r="U53" s="92" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="54" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -13306,12 +13284,16 @@
         <v>46292</v>
       </c>
       <c r="R54" s="88" t="s">
-        <v>250</v>
-      </c>
-      <c r="S54" s="105"/>
-      <c r="T54" s="88"/>
+        <v>248</v>
+      </c>
+      <c r="S54" s="105">
+        <v>30</v>
+      </c>
+      <c r="T54" s="88">
+        <v>0</v>
+      </c>
       <c r="U54" s="88" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="55" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -13323,12 +13305,12 @@
         <v>46306</v>
       </c>
       <c r="R55" s="92" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="S55" s="103"/>
       <c r="T55" s="92"/>
       <c r="U55" s="92" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="56" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -13344,12 +13326,12 @@
         <v>46306</v>
       </c>
       <c r="R56" s="103" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="S56" s="103"/>
       <c r="T56" s="92"/>
       <c r="U56" s="92" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="57" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -13357,18 +13339,20 @@
       <c r="N57" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="O57" s="44"/>
+      <c r="O57" s="44">
+        <v>5</v>
+      </c>
       <c r="P57" s="30"/>
       <c r="Q57" s="108">
         <v>46306</v>
       </c>
       <c r="R57" s="88" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="S57" s="105"/>
       <c r="T57" s="88"/>
       <c r="U57" s="88" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="58" spans="13:21" x14ac:dyDescent="0.45">
@@ -13376,94 +13360,104 @@
       <c r="N58" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="O58" s="34"/>
+      <c r="O58" s="34">
+        <v>5</v>
+      </c>
       <c r="P58" s="30"/>
       <c r="Q58" s="109">
         <v>46341</v>
       </c>
       <c r="R58" s="92" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="S58" s="103"/>
       <c r="T58" s="92"/>
       <c r="U58" s="92" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="59" spans="13:21" x14ac:dyDescent="0.45">
       <c r="M59" s="76"/>
       <c r="N59" s="34" t="s">
-        <v>189</v>
-      </c>
-      <c r="O59" s="34"/>
+        <v>145</v>
+      </c>
+      <c r="O59" s="34">
+        <v>5</v>
+      </c>
       <c r="P59" s="30"/>
       <c r="Q59" s="109">
         <v>46341</v>
       </c>
       <c r="R59" s="103" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="S59" s="103"/>
       <c r="T59" s="92"/>
       <c r="U59" s="92" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="60" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="M60" s="76"/>
       <c r="N60" s="34" t="s">
-        <v>199</v>
-      </c>
-      <c r="O60" s="34"/>
+        <v>188</v>
+      </c>
+      <c r="O60" s="34">
+        <v>3</v>
+      </c>
       <c r="P60" s="30"/>
       <c r="Q60" s="108">
         <v>46341</v>
       </c>
       <c r="R60" s="88" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="S60" s="105"/>
       <c r="T60" s="88"/>
       <c r="U60" s="88" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="61" spans="13:21" x14ac:dyDescent="0.45">
       <c r="M61" s="76"/>
       <c r="N61" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="O61" s="34"/>
+        <v>198</v>
+      </c>
+      <c r="O61" s="34">
+        <v>1</v>
+      </c>
       <c r="P61" s="30"/>
       <c r="Q61" s="109">
         <v>46355</v>
       </c>
       <c r="R61" s="92" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="S61" s="103"/>
       <c r="T61" s="92"/>
       <c r="U61" s="92" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="62" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="M62" s="76"/>
       <c r="N62" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="O62" s="36"/>
+        <v>192</v>
+      </c>
+      <c r="O62" s="36">
+        <v>1</v>
+      </c>
       <c r="P62" s="30"/>
       <c r="Q62" s="109">
         <v>46355</v>
       </c>
       <c r="R62" s="103" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="S62" s="103"/>
       <c r="T62" s="92"/>
       <c r="U62" s="92" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="63" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -13475,12 +13469,12 @@
         <v>46355</v>
       </c>
       <c r="R63" s="88" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="S63" s="105"/>
       <c r="T63" s="88"/>
       <c r="U63" s="88" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="64" spans="13:21" x14ac:dyDescent="0.45">
@@ -13492,12 +13486,12 @@
         <v>46369</v>
       </c>
       <c r="R64" s="96" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="S64" s="104"/>
       <c r="T64" s="96"/>
       <c r="U64" s="95" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="65" spans="13:21" x14ac:dyDescent="0.45">
@@ -13509,12 +13503,12 @@
         <v>46369</v>
       </c>
       <c r="R65" s="92" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="S65" s="103"/>
       <c r="T65" s="92"/>
       <c r="U65" s="91" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="66" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -13526,12 +13520,12 @@
         <v>46369</v>
       </c>
       <c r="R66" s="108" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="S66" s="103"/>
       <c r="T66" s="92"/>
       <c r="U66" s="107" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="67" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -13554,12 +13548,16 @@
         <v>46292</v>
       </c>
       <c r="R68" s="92" t="s">
-        <v>254</v>
-      </c>
-      <c r="S68" s="103"/>
-      <c r="T68" s="92"/>
+        <v>252</v>
+      </c>
+      <c r="S68" s="103">
+        <v>40</v>
+      </c>
+      <c r="T68" s="92">
+        <v>10</v>
+      </c>
       <c r="U68" s="92" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="69" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -13571,12 +13569,16 @@
         <v>46292</v>
       </c>
       <c r="R69" s="103" t="s">
-        <v>255</v>
-      </c>
-      <c r="S69" s="103"/>
-      <c r="T69" s="92"/>
+        <v>253</v>
+      </c>
+      <c r="S69" s="103">
+        <v>10</v>
+      </c>
+      <c r="T69" s="92">
+        <v>10</v>
+      </c>
       <c r="U69" s="92" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="70" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -13592,126 +13594,142 @@
         <v>46292</v>
       </c>
       <c r="R70" s="88" t="s">
-        <v>256</v>
-      </c>
-      <c r="S70" s="105"/>
-      <c r="T70" s="88"/>
+        <v>254</v>
+      </c>
+      <c r="S70" s="105">
+        <v>20</v>
+      </c>
+      <c r="T70" s="88">
+        <v>30</v>
+      </c>
       <c r="U70" s="88" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="71" spans="13:21" x14ac:dyDescent="0.45">
       <c r="M71" s="32"/>
       <c r="N71" s="44" t="s">
-        <v>137</v>
-      </c>
-      <c r="O71" s="44"/>
+        <v>138</v>
+      </c>
+      <c r="O71" s="44">
+        <v>5</v>
+      </c>
       <c r="P71" s="30"/>
       <c r="Q71" s="109">
         <v>46306</v>
       </c>
       <c r="R71" s="92" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="S71" s="103"/>
       <c r="T71" s="92"/>
       <c r="U71" s="92" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="72" spans="13:21" x14ac:dyDescent="0.45">
       <c r="M72" s="32"/>
       <c r="N72" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="O72" s="34"/>
+        <v>185</v>
+      </c>
+      <c r="O72" s="34">
+        <v>5</v>
+      </c>
       <c r="P72" s="30"/>
       <c r="Q72" s="109">
         <v>46306</v>
       </c>
       <c r="R72" s="103" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="S72" s="103"/>
       <c r="T72" s="92"/>
       <c r="U72" s="92" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="73" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="M73" s="32"/>
       <c r="N73" s="34" t="s">
-        <v>190</v>
-      </c>
-      <c r="O73" s="34"/>
+        <v>140</v>
+      </c>
+      <c r="O73" s="34">
+        <v>3</v>
+      </c>
       <c r="P73" s="30"/>
       <c r="Q73" s="108">
         <v>46306</v>
       </c>
       <c r="R73" s="88" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="S73" s="105"/>
       <c r="T73" s="88"/>
       <c r="U73" s="88" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="74" spans="13:21" x14ac:dyDescent="0.45">
       <c r="M74" s="32"/>
       <c r="N74" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="O74" s="34"/>
+        <v>189</v>
+      </c>
+      <c r="O74" s="34">
+        <v>2</v>
+      </c>
       <c r="P74" s="30"/>
       <c r="Q74" s="109">
         <v>46341</v>
       </c>
       <c r="R74" s="92" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="S74" s="103"/>
       <c r="T74" s="92"/>
       <c r="U74" s="92" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="75" spans="13:21" x14ac:dyDescent="0.45">
       <c r="M75" s="32"/>
       <c r="N75" s="34" t="s">
-        <v>186</v>
-      </c>
-      <c r="O75" s="34"/>
+        <v>178</v>
+      </c>
+      <c r="O75" s="34">
+        <v>2</v>
+      </c>
       <c r="P75" s="30"/>
       <c r="Q75" s="109">
         <v>46341</v>
       </c>
       <c r="R75" s="103" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="S75" s="103"/>
       <c r="T75" s="92"/>
       <c r="U75" s="92" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="76" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="M76" s="32"/>
       <c r="N76" s="36" t="s">
-        <v>179</v>
-      </c>
-      <c r="O76" s="36"/>
+        <v>137</v>
+      </c>
+      <c r="O76" s="36">
+        <v>1</v>
+      </c>
       <c r="P76" s="30"/>
       <c r="Q76" s="108">
         <v>46341</v>
       </c>
       <c r="R76" s="88" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="S76" s="105"/>
       <c r="T76" s="88"/>
       <c r="U76" s="88" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="77" spans="13:21" x14ac:dyDescent="0.45">
@@ -13723,12 +13741,12 @@
         <v>46355</v>
       </c>
       <c r="R77" s="92" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="S77" s="103"/>
       <c r="T77" s="92"/>
       <c r="U77" s="92" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="78" spans="13:21" x14ac:dyDescent="0.45">
@@ -13740,12 +13758,12 @@
         <v>46355</v>
       </c>
       <c r="R78" s="103" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="S78" s="103"/>
       <c r="T78" s="92"/>
       <c r="U78" s="92" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="79" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -13757,12 +13775,12 @@
         <v>46355</v>
       </c>
       <c r="R79" s="88" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="S79" s="105"/>
       <c r="T79" s="88"/>
       <c r="U79" s="88" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="80" spans="13:21" x14ac:dyDescent="0.45">
@@ -13774,12 +13792,12 @@
         <v>46369</v>
       </c>
       <c r="R80" s="96" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="S80" s="104"/>
       <c r="T80" s="96"/>
       <c r="U80" s="95" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="81" spans="13:21" x14ac:dyDescent="0.45">
@@ -13791,12 +13809,12 @@
         <v>46369</v>
       </c>
       <c r="R81" s="92" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="S81" s="103"/>
       <c r="T81" s="92"/>
       <c r="U81" s="91" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="82" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -13808,12 +13826,12 @@
         <v>46369</v>
       </c>
       <c r="R82" s="108" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="S82" s="103"/>
       <c r="T82" s="92"/>
       <c r="U82" s="107" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="83" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -13836,12 +13854,16 @@
         <v>46292</v>
       </c>
       <c r="R84" s="92" t="s">
-        <v>260</v>
-      </c>
-      <c r="S84" s="103"/>
-      <c r="T84" s="92"/>
+        <v>258</v>
+      </c>
+      <c r="S84" s="103">
+        <v>15</v>
+      </c>
+      <c r="T84" s="92">
+        <v>30</v>
+      </c>
       <c r="U84" s="92" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="85" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -13853,12 +13875,16 @@
         <v>46292</v>
       </c>
       <c r="R85" s="103" t="s">
-        <v>261</v>
-      </c>
-      <c r="S85" s="103"/>
-      <c r="T85" s="92"/>
+        <v>259</v>
+      </c>
+      <c r="S85" s="103">
+        <v>0</v>
+      </c>
+      <c r="T85" s="92">
+        <v>30</v>
+      </c>
       <c r="U85" s="92" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="86" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -13874,126 +13900,142 @@
         <v>46292</v>
       </c>
       <c r="R86" s="88" t="s">
+        <v>260</v>
+      </c>
+      <c r="S86" s="105">
+        <v>0</v>
+      </c>
+      <c r="T86" s="88">
+        <v>30</v>
+      </c>
+      <c r="U86" s="88" t="s">
         <v>262</v>
-      </c>
-      <c r="S86" s="105"/>
-      <c r="T86" s="88"/>
-      <c r="U86" s="88" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="87" spans="13:21" x14ac:dyDescent="0.45">
       <c r="M87" s="32"/>
       <c r="N87" s="45" t="s">
-        <v>184</v>
-      </c>
-      <c r="O87" s="44"/>
+        <v>183</v>
+      </c>
+      <c r="O87" s="44">
+        <v>5</v>
+      </c>
       <c r="P87" s="30"/>
       <c r="Q87" s="109">
         <v>46306</v>
       </c>
       <c r="R87" s="92" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="S87" s="103"/>
       <c r="T87" s="92"/>
       <c r="U87" s="92" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="88" spans="13:21" x14ac:dyDescent="0.45">
       <c r="M88" s="32"/>
       <c r="N88" s="32" t="s">
-        <v>91</v>
-      </c>
-      <c r="O88" s="34"/>
+        <v>197</v>
+      </c>
+      <c r="O88" s="34">
+        <v>5</v>
+      </c>
       <c r="P88" s="30"/>
       <c r="Q88" s="109">
         <v>46306</v>
       </c>
       <c r="R88" s="103" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="S88" s="103"/>
       <c r="T88" s="92"/>
       <c r="U88" s="92" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="89" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="M89" s="32"/>
       <c r="N89" s="32" t="s">
-        <v>188</v>
-      </c>
-      <c r="O89" s="34"/>
+        <v>191</v>
+      </c>
+      <c r="O89" s="34">
+        <v>5</v>
+      </c>
       <c r="P89" s="33"/>
       <c r="Q89" s="108">
         <v>46306</v>
       </c>
       <c r="R89" s="88" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="S89" s="105"/>
       <c r="T89" s="88"/>
       <c r="U89" s="88" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="90" spans="13:21" x14ac:dyDescent="0.45">
       <c r="M90" s="32"/>
       <c r="N90" s="32" t="s">
-        <v>196</v>
-      </c>
-      <c r="O90" s="34"/>
+        <v>91</v>
+      </c>
+      <c r="O90" s="34">
+        <v>1</v>
+      </c>
       <c r="P90" s="30"/>
       <c r="Q90" s="109">
         <v>46341</v>
       </c>
       <c r="R90" s="92" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="S90" s="103"/>
       <c r="T90" s="92"/>
       <c r="U90" s="92" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="91" spans="13:21" x14ac:dyDescent="0.45">
       <c r="M91" s="32"/>
       <c r="N91" s="32" t="s">
-        <v>198</v>
-      </c>
-      <c r="O91" s="34"/>
+        <v>187</v>
+      </c>
+      <c r="O91" s="34">
+        <v>1</v>
+      </c>
       <c r="P91" s="30"/>
       <c r="Q91" s="109">
         <v>46341</v>
       </c>
       <c r="R91" s="103" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="S91" s="103"/>
       <c r="T91" s="92"/>
       <c r="U91" s="92" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="92" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="M92" s="32"/>
       <c r="N92" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="O92" s="36"/>
+        <v>195</v>
+      </c>
+      <c r="O92" s="36">
+        <v>1</v>
+      </c>
       <c r="P92" s="30"/>
       <c r="Q92" s="108">
         <v>46341</v>
       </c>
       <c r="R92" s="88" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="S92" s="105"/>
       <c r="T92" s="88"/>
       <c r="U92" s="88" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="93" spans="13:21" x14ac:dyDescent="0.45">
@@ -14005,12 +14047,12 @@
         <v>46355</v>
       </c>
       <c r="R93" s="92" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="S93" s="103"/>
       <c r="T93" s="92"/>
       <c r="U93" s="92" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="94" spans="13:21" x14ac:dyDescent="0.45">
@@ -14022,12 +14064,12 @@
         <v>46355</v>
       </c>
       <c r="R94" s="103" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="S94" s="103"/>
       <c r="T94" s="92"/>
       <c r="U94" s="92" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="95" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -14039,12 +14081,12 @@
         <v>46355</v>
       </c>
       <c r="R95" s="88" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="S95" s="105"/>
       <c r="T95" s="88"/>
       <c r="U95" s="88" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="96" spans="13:21" x14ac:dyDescent="0.45">
@@ -14056,12 +14098,12 @@
         <v>46369</v>
       </c>
       <c r="R96" s="96" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="S96" s="104"/>
       <c r="T96" s="96"/>
       <c r="U96" s="95" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="97" spans="13:21" x14ac:dyDescent="0.45">
@@ -14073,12 +14115,12 @@
         <v>46369</v>
       </c>
       <c r="R97" s="92" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="S97" s="103"/>
       <c r="T97" s="92"/>
       <c r="U97" s="91" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="98" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -14090,12 +14132,12 @@
         <v>46369</v>
       </c>
       <c r="R98" s="108" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="S98" s="103"/>
       <c r="T98" s="92"/>
       <c r="U98" s="107" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="99" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -14118,12 +14160,16 @@
         <v>46292</v>
       </c>
       <c r="R100" s="54" t="s">
-        <v>265</v>
-      </c>
-      <c r="S100" s="44"/>
-      <c r="T100" s="54"/>
+        <v>263</v>
+      </c>
+      <c r="S100" s="44">
+        <v>5</v>
+      </c>
+      <c r="T100" s="54">
+        <v>35</v>
+      </c>
       <c r="U100" s="44" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="101" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -14135,12 +14181,16 @@
         <v>46292</v>
       </c>
       <c r="R101" s="232" t="s">
+        <v>264</v>
+      </c>
+      <c r="S101" s="36">
+        <v>0</v>
+      </c>
+      <c r="T101" s="28">
+        <v>30</v>
+      </c>
+      <c r="U101" s="233" t="s">
         <v>266</v>
-      </c>
-      <c r="S101" s="36"/>
-      <c r="T101" s="28"/>
-      <c r="U101" s="233" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="102" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -14156,12 +14206,12 @@
         <v>46306</v>
       </c>
       <c r="R102" s="54" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="S102" s="44"/>
       <c r="T102" s="54"/>
       <c r="U102" s="44" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="103" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -14169,81 +14219,89 @@
       <c r="N103" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="O103" s="44"/>
+      <c r="O103" s="44">
+        <v>5</v>
+      </c>
       <c r="P103" s="30"/>
       <c r="Q103" s="56">
         <v>46306</v>
       </c>
       <c r="R103" s="232" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="S103" s="36"/>
       <c r="T103" s="28"/>
       <c r="U103" s="233" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="104" spans="13:21" x14ac:dyDescent="0.45">
       <c r="M104" s="32"/>
       <c r="N104" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="O104" s="34"/>
+        <v>182</v>
+      </c>
+      <c r="O104" s="34">
+        <v>5</v>
+      </c>
       <c r="P104" s="33"/>
       <c r="Q104" s="57">
         <v>46341</v>
       </c>
       <c r="R104" s="54" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="S104" s="44"/>
       <c r="T104" s="54"/>
       <c r="U104" s="44" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="105" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="M105" s="32"/>
       <c r="N105" s="32" t="s">
-        <v>181</v>
-      </c>
-      <c r="O105" s="34"/>
+        <v>180</v>
+      </c>
+      <c r="O105" s="34">
+        <v>1</v>
+      </c>
       <c r="P105" s="30"/>
       <c r="Q105" s="56">
         <v>46341</v>
       </c>
       <c r="R105" s="232" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="S105" s="36"/>
       <c r="T105" s="28"/>
       <c r="U105" s="233" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="106" spans="13:21" x14ac:dyDescent="0.45">
       <c r="M106" s="32"/>
       <c r="N106" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="O106" s="34"/>
+        <v>190</v>
+      </c>
+      <c r="O106" s="34">
+        <v>1</v>
+      </c>
       <c r="P106" s="30"/>
       <c r="Q106" s="57">
         <v>46355</v>
       </c>
       <c r="R106" s="54" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="S106" s="44"/>
       <c r="T106" s="54"/>
       <c r="U106" s="44" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="107" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="M107" s="32"/>
       <c r="N107" s="29" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="O107" s="36"/>
       <c r="P107" s="30"/>
@@ -14251,12 +14309,12 @@
         <v>46355</v>
       </c>
       <c r="R107" s="232" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="S107" s="36"/>
       <c r="T107" s="28"/>
       <c r="U107" s="233" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="108" spans="13:21" x14ac:dyDescent="0.45">
@@ -14268,12 +14326,12 @@
         <v>46369</v>
       </c>
       <c r="R108" s="54" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="S108" s="44"/>
       <c r="T108" s="54"/>
       <c r="U108" s="44" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="109" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -14285,12 +14343,12 @@
         <v>46369</v>
       </c>
       <c r="R109" s="232" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="S109" s="36"/>
       <c r="T109" s="28"/>
       <c r="U109" s="233" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="110" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.5">
@@ -14325,6 +14383,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N87:O92">
+    <sortCondition descending="1" ref="O87:O92"/>
+  </sortState>
   <mergeCells count="3">
     <mergeCell ref="M2:U2"/>
     <mergeCell ref="N3:O3"/>
@@ -14365,67 +14426,67 @@
     <row r="1" spans="1:22" s="19" customFormat="1" ht="4.9000000000000004" customHeight="1" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="19"/>
-      <c r="B2" s="252" t="s">
+      <c r="B2" s="254" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="253"/>
-      <c r="D2" s="253"/>
-      <c r="E2" s="253"/>
-      <c r="F2" s="253"/>
-      <c r="G2" s="253"/>
-      <c r="H2" s="253"/>
-      <c r="I2" s="253"/>
-      <c r="J2" s="253"/>
-      <c r="K2" s="254"/>
+      <c r="C2" s="255"/>
+      <c r="D2" s="255"/>
+      <c r="E2" s="255"/>
+      <c r="F2" s="255"/>
+      <c r="G2" s="255"/>
+      <c r="H2" s="255"/>
+      <c r="I2" s="255"/>
+      <c r="J2" s="255"/>
+      <c r="K2" s="256"/>
       <c r="L2" s="19"/>
-      <c r="M2" s="252" t="s">
+      <c r="M2" s="254" t="s">
         <v>130</v>
       </c>
-      <c r="N2" s="253"/>
-      <c r="O2" s="253"/>
-      <c r="P2" s="253"/>
-      <c r="Q2" s="253"/>
-      <c r="R2" s="253"/>
-      <c r="S2" s="253"/>
-      <c r="T2" s="253"/>
-      <c r="U2" s="253"/>
-      <c r="V2" s="254"/>
+      <c r="N2" s="255"/>
+      <c r="O2" s="255"/>
+      <c r="P2" s="255"/>
+      <c r="Q2" s="255"/>
+      <c r="R2" s="255"/>
+      <c r="S2" s="255"/>
+      <c r="T2" s="255"/>
+      <c r="U2" s="255"/>
+      <c r="V2" s="256"/>
     </row>
     <row r="3" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="19"/>
-      <c r="B3" s="255" t="s">
+      <c r="B3" s="257" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="248"/>
-      <c r="D3" s="248"/>
-      <c r="E3" s="248"/>
+      <c r="C3" s="250"/>
+      <c r="D3" s="250"/>
+      <c r="E3" s="250"/>
       <c r="F3" s="112"/>
       <c r="G3" s="112" t="s">
         <v>57</v>
       </c>
-      <c r="H3" s="256" t="s">
+      <c r="H3" s="258" t="s">
         <v>56</v>
       </c>
-      <c r="I3" s="256"/>
-      <c r="J3" s="256"/>
-      <c r="K3" s="257"/>
+      <c r="I3" s="258"/>
+      <c r="J3" s="258"/>
+      <c r="K3" s="259"/>
       <c r="L3" s="19"/>
-      <c r="M3" s="255" t="s">
+      <c r="M3" s="257" t="s">
         <v>58</v>
       </c>
-      <c r="N3" s="248"/>
-      <c r="O3" s="248"/>
-      <c r="P3" s="248"/>
+      <c r="N3" s="250"/>
+      <c r="O3" s="250"/>
+      <c r="P3" s="250"/>
       <c r="Q3" s="112"/>
       <c r="R3" s="112" t="s">
         <v>57</v>
       </c>
-      <c r="S3" s="256" t="s">
+      <c r="S3" s="258" t="s">
         <v>56</v>
       </c>
-      <c r="T3" s="256"/>
-      <c r="U3" s="256"/>
-      <c r="V3" s="257"/>
+      <c r="T3" s="258"/>
+      <c r="U3" s="258"/>
+      <c r="V3" s="259"/>
     </row>
     <row r="4" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="111"/>
